--- a/dataset2026.xlsx
+++ b/dataset2026.xlsx
@@ -724,34 +724,34 @@
     <t>individual_indicator2</t>
   </si>
   <si>
-    <t>wait1</t>
-  </si>
-  <si>
-    <t>wait2</t>
-  </si>
-  <si>
-    <t>message1</t>
-  </si>
-  <si>
-    <t>message2</t>
-  </si>
-  <si>
     <t>threat1</t>
   </si>
   <si>
     <t>threat2</t>
   </si>
   <si>
+    <t>sentiment1</t>
+  </si>
+  <si>
+    <t>sentiment2</t>
+  </si>
+  <si>
+    <t>message1</t>
+  </si>
+  <si>
     <t>character1</t>
+  </si>
+  <si>
+    <t>message2</t>
   </si>
   <si>
     <t>character2</t>
   </si>
   <si>
-    <t>sentiment1</t>
+    <t>wait1</t>
   </si>
   <si>
-    <t>sentiment2</t>
+    <t>wait2</t>
   </si>
   <si>
     <t>2023.12.14</t>
@@ -3189,22 +3189,13 @@
         <v>0</v>
       </c>
       <c r="IE2">
-        <v>1</v>
-      </c>
-      <c r="IF2">
         <v>0</v>
       </c>
       <c r="IG2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH2">
-        <v>0</v>
-      </c>
-      <c r="II2">
         <v>29</v>
-      </c>
-      <c r="IJ2">
-        <v>0</v>
       </c>
       <c r="IK2">
         <v>0</v>
@@ -3613,23 +3604,14 @@
       <c r="IE3">
         <v>1</v>
       </c>
-      <c r="IF3">
-        <v>0</v>
-      </c>
       <c r="IG3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH3">
-        <v>0</v>
-      </c>
-      <c r="II3">
         <v>23</v>
       </c>
-      <c r="IJ3">
-        <v>0</v>
-      </c>
       <c r="IK3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:246">
@@ -4033,22 +4015,13 @@
         <v>0</v>
       </c>
       <c r="IE4">
-        <v>1</v>
-      </c>
-      <c r="IF4">
         <v>0</v>
       </c>
       <c r="IG4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH4">
-        <v>0</v>
-      </c>
-      <c r="II4">
         <v>16</v>
-      </c>
-      <c r="IJ4">
-        <v>0</v>
       </c>
       <c r="IK4">
         <v>0</v>
@@ -4448,22 +4421,13 @@
       <c r="ID5">
         <v>0</v>
       </c>
-      <c r="IE5">
-        <v>0</v>
-      </c>
-      <c r="IF5">
-        <v>0</v>
-      </c>
-      <c r="IG5">
-        <v>0</v>
-      </c>
-      <c r="IH5">
-        <v>0</v>
-      </c>
       <c r="II5">
         <v>0</v>
       </c>
       <c r="IJ5">
+        <v>0</v>
+      </c>
+      <c r="IL5">
         <v>0</v>
       </c>
     </row>
@@ -4871,28 +4835,19 @@
         <v>0</v>
       </c>
       <c r="ID6">
-        <v>1</v>
-      </c>
-      <c r="IE6">
         <v>0</v>
       </c>
       <c r="IF6">
-        <v>1</v>
-      </c>
-      <c r="IG6">
-        <v>0</v>
-      </c>
-      <c r="IH6">
         <v>0</v>
       </c>
       <c r="II6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IJ6">
         <v>52</v>
       </c>
       <c r="IL6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:246">
@@ -5289,22 +5244,13 @@
       <c r="ID7">
         <v>0</v>
       </c>
-      <c r="IE7">
-        <v>0</v>
-      </c>
-      <c r="IF7">
-        <v>0</v>
-      </c>
-      <c r="IG7">
-        <v>0</v>
-      </c>
-      <c r="IH7">
-        <v>0</v>
-      </c>
       <c r="II7">
         <v>0</v>
       </c>
       <c r="IJ7">
+        <v>0</v>
+      </c>
+      <c r="IL7">
         <v>0</v>
       </c>
     </row>
@@ -5712,28 +5658,19 @@
         <v>0</v>
       </c>
       <c r="ID8">
-        <v>1</v>
-      </c>
-      <c r="IE8">
         <v>0</v>
       </c>
       <c r="IF8">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="II8">
         <v>7</v>
-      </c>
-      <c r="IG8">
-        <v>0</v>
-      </c>
-      <c r="IH8">
-        <v>0</v>
-      </c>
-      <c r="II8">
-        <v>0</v>
       </c>
       <c r="IJ8">
         <v>433</v>
       </c>
       <c r="IL8">
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:246">
@@ -6140,28 +6077,19 @@
         <v>0</v>
       </c>
       <c r="ID9">
-        <v>-1</v>
-      </c>
-      <c r="IE9">
         <v>0</v>
       </c>
       <c r="IF9">
+        <v>0.5</v>
+      </c>
+      <c r="II9">
         <v>12</v>
-      </c>
-      <c r="IG9">
-        <v>0</v>
-      </c>
-      <c r="IH9">
-        <v>0</v>
-      </c>
-      <c r="II9">
-        <v>0</v>
       </c>
       <c r="IJ9">
         <v>527</v>
       </c>
       <c r="IL9">
-        <v>0.5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:246">
@@ -6568,28 +6496,19 @@
         <v>0</v>
       </c>
       <c r="ID10">
-        <v>-1</v>
-      </c>
-      <c r="IE10">
         <v>0</v>
       </c>
       <c r="IF10">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="II10">
         <v>14</v>
-      </c>
-      <c r="IG10">
-        <v>0</v>
-      </c>
-      <c r="IH10">
-        <v>0</v>
-      </c>
-      <c r="II10">
-        <v>0</v>
       </c>
       <c r="IJ10">
         <v>202</v>
       </c>
       <c r="IL10">
-        <v>-0.2857142857142857</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:246">
@@ -6993,25 +6912,16 @@
         <v>0</v>
       </c>
       <c r="IE11">
-        <v>3</v>
-      </c>
-      <c r="IF11">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="IG11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="IH11">
-        <v>0</v>
-      </c>
-      <c r="II11">
         <v>140</v>
       </c>
-      <c r="IJ11">
-        <v>0</v>
-      </c>
       <c r="IK11">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:246">
@@ -7417,23 +7327,14 @@
       <c r="IE12">
         <v>1</v>
       </c>
-      <c r="IF12">
-        <v>0</v>
-      </c>
       <c r="IG12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH12">
-        <v>0</v>
-      </c>
-      <c r="II12">
-        <v>3</v>
-      </c>
-      <c r="IJ12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="IK12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:246">
@@ -7839,23 +7740,14 @@
       <c r="IE13">
         <v>1</v>
       </c>
-      <c r="IF13">
-        <v>0</v>
-      </c>
       <c r="IG13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH13">
-        <v>0</v>
-      </c>
-      <c r="II13">
-        <v>3</v>
-      </c>
-      <c r="IJ13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="IK13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:246">
@@ -8283,19 +8175,19 @@
         <v>0</v>
       </c>
       <c r="IE14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="IF14">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="IG14">
+        <v>2</v>
+      </c>
+      <c r="IH14">
+        <v>44</v>
+      </c>
+      <c r="II14">
         <v>6</v>
-      </c>
-      <c r="IG14">
-        <v>0</v>
-      </c>
-      <c r="IH14">
-        <v>0</v>
-      </c>
-      <c r="II14">
-        <v>44</v>
       </c>
       <c r="IJ14">
         <v>429</v>
@@ -8304,7 +8196,7 @@
         <v>0</v>
       </c>
       <c r="IL14">
-        <v>1.333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:246">
@@ -8732,19 +8624,19 @@
         <v>0</v>
       </c>
       <c r="IE15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="IF15">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="IG15">
+        <v>2</v>
+      </c>
+      <c r="IH15">
+        <v>9</v>
+      </c>
+      <c r="II15">
         <v>6</v>
-      </c>
-      <c r="IG15">
-        <v>0</v>
-      </c>
-      <c r="IH15">
-        <v>0</v>
-      </c>
-      <c r="II15">
-        <v>9</v>
       </c>
       <c r="IJ15">
         <v>110</v>
@@ -8753,7 +8645,7 @@
         <v>0</v>
       </c>
       <c r="IL15">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:246">
@@ -9178,31 +9070,31 @@
         <v>0</v>
       </c>
       <c r="ID16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IE16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="IF16">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="IG16">
+        <v>1</v>
+      </c>
+      <c r="IH16">
+        <v>64</v>
+      </c>
+      <c r="II16">
         <v>7</v>
-      </c>
-      <c r="IG16">
-        <v>0</v>
-      </c>
-      <c r="IH16">
-        <v>0</v>
-      </c>
-      <c r="II16">
-        <v>64</v>
       </c>
       <c r="IJ16">
         <v>510</v>
       </c>
       <c r="IK16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="IL16">
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:246">
@@ -9587,24 +9479,6 @@
       <c r="ID17">
         <v>0</v>
       </c>
-      <c r="IE17">
-        <v>0</v>
-      </c>
-      <c r="IF17">
-        <v>0</v>
-      </c>
-      <c r="IG17">
-        <v>0</v>
-      </c>
-      <c r="IH17">
-        <v>0</v>
-      </c>
-      <c r="II17">
-        <v>0</v>
-      </c>
-      <c r="IJ17">
-        <v>0</v>
-      </c>
     </row>
     <row r="18" spans="1:246">
       <c r="A18" t="s">
@@ -9988,24 +9862,6 @@
       <c r="ID18">
         <v>0</v>
       </c>
-      <c r="IE18">
-        <v>0</v>
-      </c>
-      <c r="IF18">
-        <v>0</v>
-      </c>
-      <c r="IG18">
-        <v>0</v>
-      </c>
-      <c r="IH18">
-        <v>0</v>
-      </c>
-      <c r="II18">
-        <v>0</v>
-      </c>
-      <c r="IJ18">
-        <v>0</v>
-      </c>
     </row>
     <row r="19" spans="1:246">
       <c r="A19" t="s">
@@ -10389,24 +10245,6 @@
       <c r="ID19">
         <v>0</v>
       </c>
-      <c r="IE19">
-        <v>0</v>
-      </c>
-      <c r="IF19">
-        <v>0</v>
-      </c>
-      <c r="IG19">
-        <v>0</v>
-      </c>
-      <c r="IH19">
-        <v>0</v>
-      </c>
-      <c r="II19">
-        <v>0</v>
-      </c>
-      <c r="IJ19">
-        <v>0</v>
-      </c>
     </row>
     <row r="20" spans="1:246">
       <c r="A20" t="s">
@@ -10796,22 +10634,13 @@
       <c r="ID20">
         <v>0</v>
       </c>
-      <c r="IE20">
-        <v>0</v>
-      </c>
-      <c r="IF20">
-        <v>0</v>
-      </c>
       <c r="IG20">
         <v>0</v>
       </c>
       <c r="IH20">
         <v>0</v>
       </c>
-      <c r="II20">
-        <v>0</v>
-      </c>
-      <c r="IJ20">
+      <c r="IK20">
         <v>0</v>
       </c>
     </row>
@@ -11216,25 +11045,16 @@
         <v>0</v>
       </c>
       <c r="IE21">
-        <v>1</v>
-      </c>
-      <c r="IF21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IG21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH21">
-        <v>0</v>
-      </c>
-      <c r="II21">
         <v>78</v>
       </c>
-      <c r="IJ21">
-        <v>0</v>
-      </c>
       <c r="IK21">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:246">
@@ -11625,22 +11445,13 @@
       <c r="ID22">
         <v>0</v>
       </c>
-      <c r="IE22">
-        <v>0</v>
-      </c>
-      <c r="IF22">
-        <v>0</v>
-      </c>
       <c r="IG22">
         <v>0</v>
       </c>
       <c r="IH22">
         <v>0</v>
       </c>
-      <c r="II22">
-        <v>0</v>
-      </c>
-      <c r="IJ22">
+      <c r="IK22">
         <v>0</v>
       </c>
     </row>
@@ -12044,22 +11855,13 @@
       <c r="ID23">
         <v>0</v>
       </c>
-      <c r="IE23">
-        <v>1</v>
-      </c>
-      <c r="IF23">
-        <v>0</v>
-      </c>
       <c r="IG23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH23">
-        <v>0</v>
-      </c>
-      <c r="II23">
-        <v>1</v>
-      </c>
-      <c r="IJ23">
+        <v>1</v>
+      </c>
+      <c r="IK23">
         <v>0</v>
       </c>
     </row>
@@ -12464,22 +12266,13 @@
         <v>0</v>
       </c>
       <c r="IE24">
-        <v>1</v>
-      </c>
-      <c r="IF24">
         <v>0</v>
       </c>
       <c r="IG24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH24">
-        <v>0</v>
-      </c>
-      <c r="II24">
         <v>40</v>
-      </c>
-      <c r="IJ24">
-        <v>0</v>
       </c>
       <c r="IK24">
         <v>0</v>
@@ -12880,7 +12673,7 @@
         <v>1</v>
       </c>
       <c r="IC25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ID25">
         <v>0</v>
@@ -12888,20 +12681,11 @@
       <c r="IE25">
         <v>1</v>
       </c>
-      <c r="IF25">
-        <v>0</v>
-      </c>
       <c r="IG25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH25">
-        <v>0</v>
-      </c>
-      <c r="II25">
         <v>30</v>
-      </c>
-      <c r="IJ25">
-        <v>0</v>
       </c>
       <c r="IK25">
         <v>1</v>
@@ -13332,19 +13116,19 @@
         <v>0</v>
       </c>
       <c r="IE26">
+        <v>0</v>
+      </c>
+      <c r="IF26">
+        <v>0</v>
+      </c>
+      <c r="IG26">
         <v>9</v>
       </c>
-      <c r="IF26">
+      <c r="IH26">
+        <v>190</v>
+      </c>
+      <c r="II26">
         <v>6</v>
-      </c>
-      <c r="IG26">
-        <v>0</v>
-      </c>
-      <c r="IH26">
-        <v>0</v>
-      </c>
-      <c r="II26">
-        <v>190</v>
       </c>
       <c r="IJ26">
         <v>135</v>
@@ -13781,28 +13565,28 @@
         <v>0</v>
       </c>
       <c r="IE27">
+        <v>0.375</v>
+      </c>
+      <c r="IF27">
+        <v>0.25</v>
+      </c>
+      <c r="IG27">
         <v>8</v>
       </c>
-      <c r="IF27">
-        <v>4</v>
-      </c>
-      <c r="IG27">
-        <v>0</v>
-      </c>
       <c r="IH27">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="II27">
-        <v>199</v>
+        <v>4</v>
       </c>
       <c r="IJ27">
         <v>52</v>
       </c>
       <c r="IK27">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="IL27">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:246">
@@ -14230,19 +14014,19 @@
         <v>0</v>
       </c>
       <c r="IE28">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="IF28">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="IG28">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="IH28">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="II28">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="IJ28">
         <v>23</v>
@@ -14676,31 +14460,31 @@
         <v>0</v>
       </c>
       <c r="ID29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IE29">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="IF29">
+        <v>1.571428571428571</v>
+      </c>
+      <c r="IG29">
         <v>9</v>
       </c>
-      <c r="IF29">
+      <c r="IH29">
+        <v>285</v>
+      </c>
+      <c r="II29">
         <v>7</v>
-      </c>
-      <c r="IG29">
-        <v>0</v>
-      </c>
-      <c r="IH29">
-        <v>0</v>
-      </c>
-      <c r="II29">
-        <v>285</v>
       </c>
       <c r="IJ29">
         <v>255</v>
       </c>
       <c r="IK29">
-        <v>0.1111111111111111</v>
+        <v>0</v>
       </c>
       <c r="IL29">
-        <v>1.571428571428571</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:246">
@@ -15125,31 +14909,31 @@
         <v>0</v>
       </c>
       <c r="ID30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IE30">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="IF30">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="IG30">
         <v>6</v>
       </c>
-      <c r="IF30">
-        <v>3</v>
-      </c>
-      <c r="IG30">
-        <v>0</v>
-      </c>
       <c r="IH30">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="II30">
-        <v>175</v>
+        <v>3</v>
       </c>
       <c r="IJ30">
         <v>118</v>
       </c>
       <c r="IK30">
-        <v>-0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="IL30">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:246">
@@ -15577,28 +15361,28 @@
         <v>0</v>
       </c>
       <c r="IE31">
+        <v>-0.7142857142857143</v>
+      </c>
+      <c r="IF31">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="IG31">
         <v>7</v>
       </c>
-      <c r="IF31">
+      <c r="IH31">
+        <v>82</v>
+      </c>
+      <c r="II31">
         <v>6</v>
-      </c>
-      <c r="IG31">
-        <v>0</v>
-      </c>
-      <c r="IH31">
-        <v>0</v>
-      </c>
-      <c r="II31">
-        <v>82</v>
       </c>
       <c r="IJ31">
         <v>89</v>
       </c>
       <c r="IK31">
-        <v>-0.7142857142857143</v>
+        <v>0</v>
       </c>
       <c r="IL31">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:246">
@@ -16023,22 +15807,22 @@
         <v>0</v>
       </c>
       <c r="ID32">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="IE32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="IF32">
-        <v>4</v>
+        <v>-0.25</v>
       </c>
       <c r="IG32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH32">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="II32">
-        <v>101</v>
+        <v>4</v>
       </c>
       <c r="IJ32">
         <v>182</v>
@@ -16047,7 +15831,7 @@
         <v>0</v>
       </c>
       <c r="IL32">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="33" spans="1:246">
@@ -16450,12 +16234,6 @@
       <c r="ID33">
         <v>0</v>
       </c>
-      <c r="IE33">
-        <v>0</v>
-      </c>
-      <c r="IF33">
-        <v>0</v>
-      </c>
       <c r="IG33">
         <v>0</v>
       </c>
@@ -16466,6 +16244,12 @@
         <v>0</v>
       </c>
       <c r="IJ33">
+        <v>0</v>
+      </c>
+      <c r="IK33">
+        <v>0</v>
+      </c>
+      <c r="IL33">
         <v>0</v>
       </c>
     </row>
@@ -16891,31 +16675,31 @@
         <v>0</v>
       </c>
       <c r="ID34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IE34">
-        <v>3</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="IF34">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="IG34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="IH34">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="II34">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="IJ34">
         <v>87</v>
       </c>
       <c r="IK34">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="IL34">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:246">
@@ -17343,28 +17127,28 @@
         <v>0</v>
       </c>
       <c r="IE35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="IF35">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="IG35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="IH35">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="II35">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="IJ35">
         <v>8</v>
       </c>
       <c r="IK35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IL35">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:246">
@@ -17792,28 +17576,28 @@
         <v>0</v>
       </c>
       <c r="IE36">
-        <v>3</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="IF36">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="IG36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="IH36">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="II36">
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="IJ36">
         <v>76</v>
       </c>
       <c r="IK36">
-        <v>-0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="IL36">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:246">
@@ -18241,19 +18025,19 @@
         <v>0</v>
       </c>
       <c r="IE37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="IF37">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="IG37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH37">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="II37">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="IJ37">
         <v>45</v>
@@ -18647,24 +18431,6 @@
       <c r="ID38">
         <v>0</v>
       </c>
-      <c r="IE38">
-        <v>0</v>
-      </c>
-      <c r="IF38">
-        <v>0</v>
-      </c>
-      <c r="IG38">
-        <v>0</v>
-      </c>
-      <c r="IH38">
-        <v>0</v>
-      </c>
-      <c r="II38">
-        <v>0</v>
-      </c>
-      <c r="IJ38">
-        <v>0</v>
-      </c>
     </row>
     <row r="39" spans="1:246">
       <c r="A39" t="s">
@@ -19048,24 +18814,6 @@
       <c r="ID39">
         <v>0</v>
       </c>
-      <c r="IE39">
-        <v>0</v>
-      </c>
-      <c r="IF39">
-        <v>0</v>
-      </c>
-      <c r="IG39">
-        <v>0</v>
-      </c>
-      <c r="IH39">
-        <v>0</v>
-      </c>
-      <c r="II39">
-        <v>0</v>
-      </c>
-      <c r="IJ39">
-        <v>0</v>
-      </c>
     </row>
     <row r="40" spans="1:246">
       <c r="A40" t="s">
@@ -19449,24 +19197,6 @@
       <c r="ID40">
         <v>0</v>
       </c>
-      <c r="IE40">
-        <v>0</v>
-      </c>
-      <c r="IF40">
-        <v>0</v>
-      </c>
-      <c r="IG40">
-        <v>0</v>
-      </c>
-      <c r="IH40">
-        <v>0</v>
-      </c>
-      <c r="II40">
-        <v>0</v>
-      </c>
-      <c r="IJ40">
-        <v>0</v>
-      </c>
     </row>
     <row r="41" spans="1:246">
       <c r="A41" t="s">
@@ -19868,12 +19598,6 @@
       <c r="ID41">
         <v>0</v>
       </c>
-      <c r="IE41">
-        <v>0</v>
-      </c>
-      <c r="IF41">
-        <v>0</v>
-      </c>
       <c r="IG41">
         <v>0</v>
       </c>
@@ -19884,6 +19608,12 @@
         <v>0</v>
       </c>
       <c r="IJ41">
+        <v>0</v>
+      </c>
+      <c r="IK41">
+        <v>0</v>
+      </c>
+      <c r="IL41">
         <v>0</v>
       </c>
     </row>
@@ -20312,28 +20042,28 @@
         <v>0</v>
       </c>
       <c r="IE42">
-        <v>4</v>
+        <v>0.25</v>
       </c>
       <c r="IF42">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="IG42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="IH42">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="II42">
-        <v>208</v>
+        <v>2</v>
       </c>
       <c r="IJ42">
         <v>23</v>
       </c>
       <c r="IK42">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="IL42">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:246">
@@ -20751,23 +20481,23 @@
       <c r="IE43">
         <v>1</v>
       </c>
-      <c r="IF43">
-        <v>0</v>
-      </c>
       <c r="IG43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH43">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="II43">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="IJ43">
         <v>0</v>
       </c>
       <c r="IK43">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="IL43">
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:246">
@@ -21195,19 +20925,19 @@
         <v>0</v>
       </c>
       <c r="IE44">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="IF44">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="IG44">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="IH44">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="II44">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="IJ44">
         <v>68</v>
@@ -21644,25 +21374,25 @@
         <v>0</v>
       </c>
       <c r="IE45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="IF45">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="IG45">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="IH45">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="II45">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="IJ45">
         <v>106</v>
       </c>
       <c r="IK45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IL45">
         <v>0</v>
@@ -22093,28 +21823,28 @@
         <v>0</v>
       </c>
       <c r="IE46">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="IF46">
-        <v>4</v>
+        <v>1.25</v>
       </c>
       <c r="IG46">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="IH46">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="II46">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="IJ46">
         <v>133</v>
       </c>
       <c r="IK46">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="IL46">
-        <v>1.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:246">
@@ -22515,7 +22245,7 @@
         <v>4</v>
       </c>
       <c r="HV47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="HW47">
         <v>3</v>
@@ -22527,7 +22257,7 @@
         <v>1</v>
       </c>
       <c r="HZ47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IA47">
         <v>1</v>
@@ -22542,19 +22272,19 @@
         <v>0</v>
       </c>
       <c r="IE47">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="IF47">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="IG47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH47">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="II47">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="IJ47">
         <v>6</v>
@@ -22964,7 +22694,7 @@
         <v>4</v>
       </c>
       <c r="HV48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="HW48">
         <v>2</v>
@@ -22976,7 +22706,7 @@
         <v>1</v>
       </c>
       <c r="HZ48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IA48">
         <v>1</v>
@@ -22991,25 +22721,25 @@
         <v>0</v>
       </c>
       <c r="IE48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IF48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IG48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH48">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="II48">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="IJ48">
         <v>8</v>
       </c>
       <c r="IK48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IL48">
         <v>0</v>
@@ -23434,25 +23164,25 @@
         <v>0</v>
       </c>
       <c r="IE49">
-        <v>2</v>
-      </c>
-      <c r="IF49">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="IG49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH49">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="II49">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="IJ49">
         <v>0</v>
       </c>
       <c r="IK49">
-        <v>0.5</v>
+        <v>0</v>
+      </c>
+      <c r="IL49">
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:246">
@@ -23877,28 +23607,28 @@
         <v>0</v>
       </c>
       <c r="IE50">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="IF50">
+        <v>1.4</v>
+      </c>
+      <c r="IG50">
+        <v>2</v>
+      </c>
+      <c r="IH50">
+        <v>32</v>
+      </c>
+      <c r="II50">
         <v>5</v>
-      </c>
-      <c r="IG50">
-        <v>0</v>
-      </c>
-      <c r="IH50">
-        <v>0</v>
-      </c>
-      <c r="II50">
-        <v>32</v>
       </c>
       <c r="IJ50">
         <v>181</v>
       </c>
       <c r="IK50">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="IL50">
-        <v>1.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:246">
@@ -24320,22 +24050,22 @@
         <v>0</v>
       </c>
       <c r="ID51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IE51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IF51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="IG51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="II51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="IJ51">
         <v>137</v>
@@ -24766,22 +24496,22 @@
         <v>0</v>
       </c>
       <c r="ID52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IE52">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="IF52">
+        <v>1</v>
+      </c>
+      <c r="IG52">
+        <v>3</v>
+      </c>
+      <c r="IH52">
+        <v>58</v>
+      </c>
+      <c r="II52">
         <v>5</v>
-      </c>
-      <c r="IG52">
-        <v>0</v>
-      </c>
-      <c r="IH52">
-        <v>0</v>
-      </c>
-      <c r="II52">
-        <v>58</v>
       </c>
       <c r="IJ52">
         <v>214</v>
@@ -25191,25 +24921,16 @@
         <v>0</v>
       </c>
       <c r="IE53">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="IG53">
         <v>6</v>
       </c>
-      <c r="IF53">
-        <v>0</v>
-      </c>
-      <c r="IG53">
-        <v>0</v>
-      </c>
       <c r="IH53">
-        <v>0</v>
-      </c>
-      <c r="II53">
         <v>116</v>
       </c>
-      <c r="IJ53">
-        <v>0</v>
-      </c>
       <c r="IK53">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:246">
@@ -25610,25 +25331,16 @@
         <v>0</v>
       </c>
       <c r="IE54">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="IG54">
         <v>9</v>
       </c>
-      <c r="IF54">
-        <v>0</v>
-      </c>
-      <c r="IG54">
-        <v>0</v>
-      </c>
       <c r="IH54">
-        <v>0</v>
-      </c>
-      <c r="II54">
         <v>313</v>
       </c>
-      <c r="IJ54">
-        <v>0</v>
-      </c>
       <c r="IK54">
-        <v>0.4444444444444444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:246">
@@ -26029,22 +25741,13 @@
         <v>0</v>
       </c>
       <c r="IE55">
+        <v>0</v>
+      </c>
+      <c r="IG55">
         <v>6</v>
       </c>
-      <c r="IF55">
-        <v>0</v>
-      </c>
-      <c r="IG55">
-        <v>0</v>
-      </c>
       <c r="IH55">
-        <v>0</v>
-      </c>
-      <c r="II55">
         <v>117</v>
-      </c>
-      <c r="IJ55">
-        <v>0</v>
       </c>
       <c r="IK55">
         <v>0</v>
@@ -26472,28 +26175,28 @@
         <v>0</v>
       </c>
       <c r="IE56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="IF56">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="IG56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH56">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="II56">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="IJ56">
         <v>9</v>
       </c>
       <c r="IK56">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="IL56">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:246">
@@ -26905,11 +26608,8 @@
       <c r="ID57">
         <v>0</v>
       </c>
-      <c r="IE57">
-        <v>0</v>
-      </c>
       <c r="IF57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="IG57">
         <v>0</v>
@@ -26918,13 +26618,16 @@
         <v>0</v>
       </c>
       <c r="II57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IJ57">
         <v>35</v>
       </c>
+      <c r="IK57">
+        <v>0</v>
+      </c>
       <c r="IL57">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:246">
@@ -27349,28 +27052,28 @@
         <v>0</v>
       </c>
       <c r="IE58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="IF58">
         <v>2</v>
       </c>
       <c r="IG58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH58">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="II58">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="IJ58">
         <v>54</v>
       </c>
       <c r="IK58">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="IL58">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:246">
@@ -27792,22 +27495,22 @@
         <v>0</v>
       </c>
       <c r="ID59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IE59">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="IF59">
-        <v>4</v>
+        <v>-0.75</v>
       </c>
       <c r="IG59">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH59">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="II59">
-        <v>116</v>
+        <v>4</v>
       </c>
       <c r="IJ59">
         <v>167</v>
@@ -27816,7 +27519,7 @@
         <v>0</v>
       </c>
       <c r="IL59">
-        <v>-0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:246">
@@ -28241,19 +27944,19 @@
         <v>0</v>
       </c>
       <c r="IE60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IF60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="IG60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH60">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="II60">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="IJ60">
         <v>119</v>
@@ -28262,7 +27965,7 @@
         <v>0</v>
       </c>
       <c r="IL60">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:246">
@@ -28687,28 +28390,28 @@
         <v>0</v>
       </c>
       <c r="IE61">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="IF61">
-        <v>3</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="IG61">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH61">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="II61">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="IJ61">
         <v>83</v>
       </c>
       <c r="IK61">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="IL61">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:246">
@@ -29133,25 +28836,25 @@
         <v>0</v>
       </c>
       <c r="IE62">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="IF62">
+        <v>0</v>
+      </c>
+      <c r="IG62">
         <v>7</v>
       </c>
-      <c r="IF62">
-        <v>1</v>
-      </c>
-      <c r="IG62">
-        <v>0</v>
-      </c>
       <c r="IH62">
-        <v>0</v>
+        <v>314</v>
       </c>
       <c r="II62">
-        <v>314</v>
+        <v>1</v>
       </c>
       <c r="IJ62">
         <v>14</v>
       </c>
       <c r="IK62">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="IL62">
         <v>0</v>
@@ -29579,28 +29282,28 @@
         <v>0</v>
       </c>
       <c r="IE63">
+        <v>1.230769230769231</v>
+      </c>
+      <c r="IF63">
+        <v>1.2</v>
+      </c>
+      <c r="IG63">
         <v>13</v>
       </c>
-      <c r="IF63">
+      <c r="IH63">
+        <v>648</v>
+      </c>
+      <c r="II63">
         <v>5</v>
-      </c>
-      <c r="IG63">
-        <v>0</v>
-      </c>
-      <c r="IH63">
-        <v>0</v>
-      </c>
-      <c r="II63">
-        <v>648</v>
       </c>
       <c r="IJ63">
         <v>109</v>
       </c>
       <c r="IK63">
-        <v>1.230769230769231</v>
+        <v>0</v>
       </c>
       <c r="IL63">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:246">
@@ -30025,19 +29728,19 @@
         <v>0</v>
       </c>
       <c r="IE64">
+        <v>0</v>
+      </c>
+      <c r="IF64">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="IG64">
         <v>7</v>
       </c>
-      <c r="IF64">
-        <v>3</v>
-      </c>
-      <c r="IG64">
-        <v>0</v>
-      </c>
       <c r="IH64">
-        <v>0</v>
+        <v>274</v>
       </c>
       <c r="II64">
-        <v>274</v>
+        <v>3</v>
       </c>
       <c r="IJ64">
         <v>39</v>
@@ -30046,7 +29749,7 @@
         <v>0</v>
       </c>
       <c r="IL64">
-        <v>2.333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:246">
@@ -30468,22 +30171,22 @@
         <v>0</v>
       </c>
       <c r="ID65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IE65">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="IF65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IG65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH65">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="II65">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="IJ65">
         <v>32</v>
@@ -30492,7 +30195,7 @@
         <v>0</v>
       </c>
       <c r="IL65">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:246">
@@ -30917,28 +30620,28 @@
         <v>0</v>
       </c>
       <c r="IE66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="IF66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="IG66">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH66">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="II66">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="IJ66">
         <v>11</v>
       </c>
       <c r="IK66">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="IL66">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:246">
@@ -31363,25 +31066,25 @@
         <v>0</v>
       </c>
       <c r="IE67">
-        <v>3</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="IF67">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="IG67">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="IH67">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="II67">
-        <v>156</v>
+        <v>2</v>
       </c>
       <c r="IJ67">
         <v>72</v>
       </c>
       <c r="IK67">
-        <v>2.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="IL67">
         <v>0</v>
@@ -31806,28 +31509,28 @@
         <v>0</v>
       </c>
       <c r="ID68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IE68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="IF68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IG68">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="IH68">
-        <v>0</v>
+        <v>268</v>
       </c>
       <c r="II68">
-        <v>268</v>
+        <v>2</v>
       </c>
       <c r="IJ68">
         <v>44</v>
       </c>
       <c r="IK68">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="IL68">
         <v>1</v>
@@ -32243,24 +31946,24 @@
         <v>0</v>
       </c>
       <c r="IE69">
-        <v>1</v>
-      </c>
-      <c r="IF69">
         <v>0</v>
       </c>
       <c r="IG69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH69">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="II69">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="IJ69">
         <v>0</v>
       </c>
       <c r="IK69">
+        <v>0</v>
+      </c>
+      <c r="IL69">
         <v>0</v>
       </c>
     </row>
@@ -32686,19 +32389,19 @@
         <v>0</v>
       </c>
       <c r="IE70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IF70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IG70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH70">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="II70">
-        <v>111</v>
+        <v>1</v>
       </c>
       <c r="IJ70">
         <v>7</v>
@@ -33132,28 +32835,28 @@
         <v>0</v>
       </c>
       <c r="IE71">
-        <v>2</v>
+        <v>-0.5</v>
       </c>
       <c r="IF71">
-        <v>2</v>
+        <v>-0.5</v>
       </c>
       <c r="IG71">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH71">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="II71">
-        <v>167</v>
+        <v>2</v>
       </c>
       <c r="IJ71">
         <v>126</v>
       </c>
       <c r="IK71">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="IL71">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:246">
@@ -33575,31 +33278,31 @@
         <v>0</v>
       </c>
       <c r="ID72">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="IE72">
-        <v>4</v>
+        <v>1.25</v>
       </c>
       <c r="IF72">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="IG72">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="IH72">
-        <v>0</v>
+        <v>364</v>
       </c>
       <c r="II72">
-        <v>364</v>
+        <v>2</v>
       </c>
       <c r="IJ72">
         <v>213</v>
       </c>
       <c r="IK72">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="IL72">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="73" spans="1:246">
@@ -34017,9 +33720,6 @@
       <c r="ID73">
         <v>0</v>
       </c>
-      <c r="IE73">
-        <v>0</v>
-      </c>
       <c r="IF73">
         <v>1</v>
       </c>
@@ -34030,13 +33730,16 @@
         <v>0</v>
       </c>
       <c r="II73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IJ73">
         <v>13</v>
       </c>
+      <c r="IK73">
+        <v>0</v>
+      </c>
       <c r="IL73">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:246">
@@ -34418,24 +34121,6 @@
       <c r="ID74">
         <v>0</v>
       </c>
-      <c r="IE74">
-        <v>0</v>
-      </c>
-      <c r="IF74">
-        <v>0</v>
-      </c>
-      <c r="IG74">
-        <v>0</v>
-      </c>
-      <c r="IH74">
-        <v>0</v>
-      </c>
-      <c r="II74">
-        <v>0</v>
-      </c>
-      <c r="IJ74">
-        <v>0</v>
-      </c>
     </row>
     <row r="75" spans="1:246">
       <c r="A75" t="s">
@@ -34816,24 +34501,6 @@
       <c r="ID75">
         <v>0</v>
       </c>
-      <c r="IE75">
-        <v>0</v>
-      </c>
-      <c r="IF75">
-        <v>0</v>
-      </c>
-      <c r="IG75">
-        <v>0</v>
-      </c>
-      <c r="IH75">
-        <v>0</v>
-      </c>
-      <c r="II75">
-        <v>0</v>
-      </c>
-      <c r="IJ75">
-        <v>0</v>
-      </c>
     </row>
     <row r="76" spans="1:246">
       <c r="A76" t="s">
@@ -35214,24 +34881,6 @@
       <c r="ID76">
         <v>0</v>
       </c>
-      <c r="IE76">
-        <v>0</v>
-      </c>
-      <c r="IF76">
-        <v>0</v>
-      </c>
-      <c r="IG76">
-        <v>0</v>
-      </c>
-      <c r="IH76">
-        <v>0</v>
-      </c>
-      <c r="II76">
-        <v>0</v>
-      </c>
-      <c r="IJ76">
-        <v>0</v>
-      </c>
     </row>
     <row r="77" spans="1:246">
       <c r="A77" t="s">
@@ -35655,19 +35304,19 @@
         <v>0</v>
       </c>
       <c r="IE77">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="IF77">
+        <v>0.4</v>
+      </c>
+      <c r="IG77">
+        <v>4</v>
+      </c>
+      <c r="IH77">
+        <v>98</v>
+      </c>
+      <c r="II77">
         <v>5</v>
-      </c>
-      <c r="IG77">
-        <v>0</v>
-      </c>
-      <c r="IH77">
-        <v>0</v>
-      </c>
-      <c r="II77">
-        <v>98</v>
       </c>
       <c r="IJ77">
         <v>240</v>
@@ -35676,7 +35325,7 @@
         <v>0</v>
       </c>
       <c r="IL77">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:246">
@@ -36101,28 +35750,28 @@
         <v>0</v>
       </c>
       <c r="IE78">
+        <v>0.8</v>
+      </c>
+      <c r="IF78">
+        <v>1.6</v>
+      </c>
+      <c r="IG78">
         <v>5</v>
       </c>
-      <c r="IF78">
+      <c r="IH78">
+        <v>347</v>
+      </c>
+      <c r="II78">
         <v>5</v>
-      </c>
-      <c r="IG78">
-        <v>0</v>
-      </c>
-      <c r="IH78">
-        <v>0</v>
-      </c>
-      <c r="II78">
-        <v>347</v>
       </c>
       <c r="IJ78">
         <v>157</v>
       </c>
       <c r="IK78">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="IL78">
-        <v>1.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:246">
@@ -36544,31 +36193,31 @@
         <v>0</v>
       </c>
       <c r="ID79">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="IE79">
-        <v>3</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="IF79">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="IG79">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="IH79">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="II79">
-        <v>147</v>
+        <v>3</v>
       </c>
       <c r="IJ79">
         <v>76</v>
       </c>
       <c r="IK79">
-        <v>2.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="IL79">
-        <v>0.3333333333333333</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="80" spans="1:246">
@@ -36990,31 +36639,31 @@
         <v>0</v>
       </c>
       <c r="ID80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IE80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="IF80">
-        <v>4</v>
+        <v>-0.75</v>
       </c>
       <c r="IG80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH80">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="II80">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="IJ80">
         <v>223</v>
       </c>
       <c r="IK80">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="IL80">
-        <v>-0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:246">
@@ -37439,28 +37088,28 @@
         <v>0</v>
       </c>
       <c r="IE81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="IF81">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="IG81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH81">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="II81">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="IJ81">
         <v>293</v>
       </c>
       <c r="IK81">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="IL81">
-        <v>3.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:246">
@@ -37885,19 +37534,19 @@
         <v>0</v>
       </c>
       <c r="IE82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IF82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IG82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH82">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="II82">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="IJ82">
         <v>45</v>
@@ -38288,24 +37937,6 @@
       <c r="ID83">
         <v>0</v>
       </c>
-      <c r="IE83">
-        <v>0</v>
-      </c>
-      <c r="IF83">
-        <v>0</v>
-      </c>
-      <c r="IG83">
-        <v>0</v>
-      </c>
-      <c r="IH83">
-        <v>0</v>
-      </c>
-      <c r="II83">
-        <v>0</v>
-      </c>
-      <c r="IJ83">
-        <v>0</v>
-      </c>
     </row>
     <row r="84" spans="1:246">
       <c r="A84" t="s">
@@ -38686,24 +38317,6 @@
       <c r="ID84">
         <v>0</v>
       </c>
-      <c r="IE84">
-        <v>0</v>
-      </c>
-      <c r="IF84">
-        <v>0</v>
-      </c>
-      <c r="IG84">
-        <v>0</v>
-      </c>
-      <c r="IH84">
-        <v>0</v>
-      </c>
-      <c r="II84">
-        <v>0</v>
-      </c>
-      <c r="IJ84">
-        <v>0</v>
-      </c>
     </row>
     <row r="85" spans="1:246">
       <c r="A85" t="s">
@@ -39084,24 +38697,6 @@
       <c r="ID85">
         <v>0</v>
       </c>
-      <c r="IE85">
-        <v>0</v>
-      </c>
-      <c r="IF85">
-        <v>0</v>
-      </c>
-      <c r="IG85">
-        <v>0</v>
-      </c>
-      <c r="IH85">
-        <v>0</v>
-      </c>
-      <c r="II85">
-        <v>0</v>
-      </c>
-      <c r="IJ85">
-        <v>0</v>
-      </c>
     </row>
     <row r="86" spans="1:246">
       <c r="A86" t="s">
@@ -39501,22 +39096,13 @@
         <v>0</v>
       </c>
       <c r="IE86">
-        <v>1</v>
-      </c>
-      <c r="IF86">
         <v>0</v>
       </c>
       <c r="IG86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH86">
-        <v>0</v>
-      </c>
-      <c r="II86">
         <v>31</v>
-      </c>
-      <c r="IJ86">
-        <v>0</v>
       </c>
       <c r="IK86">
         <v>0</v>
@@ -39922,23 +39508,14 @@
       <c r="IE87">
         <v>1</v>
       </c>
-      <c r="IF87">
-        <v>0</v>
-      </c>
       <c r="IG87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH87">
-        <v>0</v>
-      </c>
-      <c r="II87">
         <v>34</v>
       </c>
-      <c r="IJ87">
-        <v>0</v>
-      </c>
       <c r="IK87">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:246">
@@ -40326,22 +39903,13 @@
       <c r="ID88">
         <v>0</v>
       </c>
-      <c r="IE88">
-        <v>0</v>
-      </c>
-      <c r="IF88">
-        <v>0</v>
-      </c>
       <c r="IG88">
         <v>0</v>
       </c>
       <c r="IH88">
         <v>0</v>
       </c>
-      <c r="II88">
-        <v>0</v>
-      </c>
-      <c r="IJ88">
+      <c r="IK88">
         <v>0</v>
       </c>
     </row>
@@ -40764,31 +40332,31 @@
         <v>0</v>
       </c>
       <c r="ID89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IE89">
+        <v>2.2</v>
+      </c>
+      <c r="IF89">
+        <v>-0.5</v>
+      </c>
+      <c r="IG89">
         <v>5</v>
       </c>
-      <c r="IF89">
-        <v>2</v>
-      </c>
-      <c r="IG89">
-        <v>0</v>
-      </c>
       <c r="IH89">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="II89">
-        <v>319</v>
+        <v>2</v>
       </c>
       <c r="IJ89">
         <v>148</v>
       </c>
       <c r="IK89">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="IL89">
-        <v>-0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:246">
@@ -41210,28 +40778,28 @@
         <v>0</v>
       </c>
       <c r="ID90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IE90">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="IF90">
         <v>1</v>
       </c>
       <c r="IG90">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH90">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="II90">
-        <v>87</v>
+        <v>1</v>
       </c>
       <c r="IJ90">
         <v>39</v>
       </c>
       <c r="IK90">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="IL90">
         <v>1</v>
@@ -41659,28 +41227,28 @@
         <v>0</v>
       </c>
       <c r="IE91">
-        <v>3</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="IF91">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="IG91">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="IH91">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="II91">
-        <v>122</v>
+        <v>3</v>
       </c>
       <c r="IJ91">
         <v>81</v>
       </c>
       <c r="IK91">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="IL91">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:246">
@@ -42108,28 +41676,28 @@
         <v>0</v>
       </c>
       <c r="IE92">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="IF92">
+        <v>0.6</v>
+      </c>
+      <c r="IG92">
         <v>7</v>
       </c>
-      <c r="IF92">
+      <c r="IH92">
+        <v>246</v>
+      </c>
+      <c r="II92">
         <v>5</v>
-      </c>
-      <c r="IG92">
-        <v>0</v>
-      </c>
-      <c r="IH92">
-        <v>0</v>
-      </c>
-      <c r="II92">
-        <v>246</v>
       </c>
       <c r="IJ92">
         <v>190</v>
       </c>
       <c r="IK92">
-        <v>1.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="IL92">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:246">
@@ -42557,28 +42125,28 @@
         <v>0</v>
       </c>
       <c r="IE93">
+        <v>0.3</v>
+      </c>
+      <c r="IF93">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="IG93">
         <v>10</v>
       </c>
-      <c r="IF93">
-        <v>3</v>
-      </c>
-      <c r="IG93">
-        <v>0</v>
-      </c>
       <c r="IH93">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="II93">
-        <v>219</v>
+        <v>3</v>
       </c>
       <c r="IJ93">
         <v>55</v>
       </c>
       <c r="IK93">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="IL93">
-        <v>1.666666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:246">
@@ -43006,28 +42574,28 @@
         <v>0</v>
       </c>
       <c r="IE94">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="IF94">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="IG94">
         <v>13</v>
       </c>
-      <c r="IF94">
+      <c r="IH94">
+        <v>262</v>
+      </c>
+      <c r="II94">
         <v>6</v>
-      </c>
-      <c r="IG94">
-        <v>0</v>
-      </c>
-      <c r="IH94">
-        <v>0</v>
-      </c>
-      <c r="II94">
-        <v>262</v>
       </c>
       <c r="IJ94">
         <v>133</v>
       </c>
       <c r="IK94">
-        <v>0.1538461538461539</v>
+        <v>0</v>
       </c>
       <c r="IL94">
-        <v>-0.3333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:246">
@@ -43455,19 +43023,19 @@
         <v>0</v>
       </c>
       <c r="IE95">
+        <v>0</v>
+      </c>
+      <c r="IF95">
+        <v>0</v>
+      </c>
+      <c r="IG95">
         <v>5</v>
       </c>
-      <c r="IF95">
-        <v>2</v>
-      </c>
-      <c r="IG95">
-        <v>0</v>
-      </c>
       <c r="IH95">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="II95">
-        <v>121</v>
+        <v>2</v>
       </c>
       <c r="IJ95">
         <v>11</v>
@@ -43904,19 +43472,19 @@
         <v>0</v>
       </c>
       <c r="IE96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IF96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IG96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH96">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="II96">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="IJ96">
         <v>31</v>
@@ -44353,25 +43921,25 @@
         <v>0</v>
       </c>
       <c r="IE97">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="IF97">
+        <v>0</v>
+      </c>
+      <c r="IG97">
         <v>11</v>
       </c>
-      <c r="IF97">
-        <v>1</v>
-      </c>
-      <c r="IG97">
-        <v>0</v>
-      </c>
       <c r="IH97">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="II97">
-        <v>189</v>
+        <v>1</v>
       </c>
       <c r="IJ97">
         <v>6</v>
       </c>
       <c r="IK97">
-        <v>0.1818181818181818</v>
+        <v>0</v>
       </c>
       <c r="IL97">
         <v>0</v>
@@ -44778,22 +44346,13 @@
         <v>0</v>
       </c>
       <c r="IE98">
-        <v>1</v>
-      </c>
-      <c r="IF98">
         <v>0</v>
       </c>
       <c r="IG98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH98">
-        <v>0</v>
-      </c>
-      <c r="II98">
         <v>31</v>
-      </c>
-      <c r="IJ98">
-        <v>0</v>
       </c>
       <c r="IK98">
         <v>0</v>
@@ -45200,25 +44759,16 @@
         <v>0</v>
       </c>
       <c r="IE99">
-        <v>2</v>
-      </c>
-      <c r="IF99">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="IG99">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH99">
-        <v>0</v>
-      </c>
-      <c r="II99">
         <v>59</v>
       </c>
-      <c r="IJ99">
-        <v>0</v>
-      </c>
       <c r="IK99">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:246">
@@ -45622,25 +45172,16 @@
         <v>0</v>
       </c>
       <c r="IE100">
-        <v>4</v>
-      </c>
-      <c r="IF100">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="IG100">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="IH100">
-        <v>0</v>
-      </c>
-      <c r="II100">
         <v>77</v>
       </c>
-      <c r="IJ100">
-        <v>0</v>
-      </c>
       <c r="IK100">
-        <v>1.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:246">
@@ -46068,28 +45609,28 @@
         <v>0</v>
       </c>
       <c r="IE101">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="IF101">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="IG101">
+        <v>2</v>
+      </c>
+      <c r="IH101">
+        <v>42</v>
+      </c>
+      <c r="II101">
         <v>7</v>
-      </c>
-      <c r="IG101">
-        <v>0</v>
-      </c>
-      <c r="IH101">
-        <v>0</v>
-      </c>
-      <c r="II101">
-        <v>42</v>
       </c>
       <c r="IJ101">
         <v>193</v>
       </c>
       <c r="IK101">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="IL101">
-        <v>0.7142857142857143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:246">
@@ -46517,28 +46058,28 @@
         <v>0</v>
       </c>
       <c r="IE102">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="IF102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="IG102">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="IH102">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="II102">
-        <v>111</v>
+        <v>1</v>
       </c>
       <c r="IJ102">
         <v>30</v>
       </c>
       <c r="IK102">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="IL102">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:246">
@@ -46966,19 +46507,19 @@
         <v>0</v>
       </c>
       <c r="IE103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IF103">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="IG103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH103">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="II103">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="IJ103">
         <v>23</v>
@@ -46987,7 +46528,7 @@
         <v>0</v>
       </c>
       <c r="IL103">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:246">
@@ -47415,28 +46956,28 @@
         <v>0</v>
       </c>
       <c r="IE104">
-        <v>3</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="IF104">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="IG104">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="IH104">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="II104">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="IJ104">
         <v>95</v>
       </c>
       <c r="IK104">
-        <v>1.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="IL104">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:246">
@@ -47864,28 +47405,28 @@
         <v>0</v>
       </c>
       <c r="IE105">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="IF105">
         <v>1</v>
       </c>
       <c r="IG105">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="IH105">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="II105">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="IJ105">
         <v>15</v>
       </c>
       <c r="IK105">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="IL105">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:246">
@@ -48313,28 +47854,28 @@
         <v>0</v>
       </c>
       <c r="IE106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IF106">
         <v>1</v>
       </c>
       <c r="IG106">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH106">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="II106">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="IJ106">
         <v>3</v>
       </c>
       <c r="IK106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IL106">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:246">
@@ -48768,22 +48309,22 @@
         <v>1</v>
       </c>
       <c r="IG107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH107">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="II107">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="IJ107">
         <v>4</v>
       </c>
       <c r="IK107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IL107">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:246">
@@ -49211,28 +48752,28 @@
         <v>0</v>
       </c>
       <c r="IE108">
-        <v>4</v>
+        <v>1.75</v>
       </c>
       <c r="IF108">
-        <v>3</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="IG108">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="IH108">
-        <v>0</v>
+        <v>386</v>
       </c>
       <c r="II108">
-        <v>386</v>
+        <v>3</v>
       </c>
       <c r="IJ108">
         <v>185</v>
       </c>
       <c r="IK108">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="IL108">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:246">
@@ -49660,28 +49201,28 @@
         <v>0</v>
       </c>
       <c r="IE109">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="IF109">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="IG109">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="IH109">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="II109">
-        <v>191</v>
+        <v>3</v>
       </c>
       <c r="IJ109">
         <v>164</v>
       </c>
       <c r="IK109">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="IL109">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:246">
@@ -50109,19 +49650,19 @@
         <v>0</v>
       </c>
       <c r="IE110">
+        <v>0</v>
+      </c>
+      <c r="IF110">
+        <v>0.4</v>
+      </c>
+      <c r="IG110">
         <v>7</v>
       </c>
-      <c r="IF110">
+      <c r="IH110">
+        <v>124</v>
+      </c>
+      <c r="II110">
         <v>5</v>
-      </c>
-      <c r="IG110">
-        <v>0</v>
-      </c>
-      <c r="IH110">
-        <v>0</v>
-      </c>
-      <c r="II110">
-        <v>124</v>
       </c>
       <c r="IJ110">
         <v>68</v>
@@ -50130,7 +49671,7 @@
         <v>0</v>
       </c>
       <c r="IL110">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:246">
@@ -50558,25 +50099,25 @@
         <v>0</v>
       </c>
       <c r="IE111">
+        <v>1.8</v>
+      </c>
+      <c r="IF111">
+        <v>0</v>
+      </c>
+      <c r="IG111">
         <v>5</v>
       </c>
-      <c r="IF111">
+      <c r="IH111">
+        <v>64</v>
+      </c>
+      <c r="II111">
         <v>6</v>
-      </c>
-      <c r="IG111">
-        <v>0</v>
-      </c>
-      <c r="IH111">
-        <v>0</v>
-      </c>
-      <c r="II111">
-        <v>64</v>
       </c>
       <c r="IJ111">
         <v>61</v>
       </c>
       <c r="IK111">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="IL111">
         <v>0</v>
@@ -51007,28 +50548,28 @@
         <v>0</v>
       </c>
       <c r="IE112">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="IF112">
-        <v>4</v>
+        <v>0.25</v>
       </c>
       <c r="IG112">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="IH112">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="II112">
-        <v>95</v>
+        <v>4</v>
       </c>
       <c r="IJ112">
         <v>72</v>
       </c>
       <c r="IK112">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="IL112">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:246">
@@ -51413,24 +50954,6 @@
       <c r="ID113">
         <v>0</v>
       </c>
-      <c r="IE113">
-        <v>0</v>
-      </c>
-      <c r="IF113">
-        <v>0</v>
-      </c>
-      <c r="IG113">
-        <v>0</v>
-      </c>
-      <c r="IH113">
-        <v>0</v>
-      </c>
-      <c r="II113">
-        <v>0</v>
-      </c>
-      <c r="IJ113">
-        <v>0</v>
-      </c>
     </row>
     <row r="114" spans="1:246">
       <c r="A114" t="s">
@@ -51814,24 +51337,6 @@
       <c r="ID114">
         <v>0</v>
       </c>
-      <c r="IE114">
-        <v>0</v>
-      </c>
-      <c r="IF114">
-        <v>0</v>
-      </c>
-      <c r="IG114">
-        <v>0</v>
-      </c>
-      <c r="IH114">
-        <v>0</v>
-      </c>
-      <c r="II114">
-        <v>0</v>
-      </c>
-      <c r="IJ114">
-        <v>0</v>
-      </c>
     </row>
     <row r="115" spans="1:246">
       <c r="A115" t="s">
@@ -52215,24 +51720,6 @@
       <c r="ID115">
         <v>0</v>
       </c>
-      <c r="IE115">
-        <v>0</v>
-      </c>
-      <c r="IF115">
-        <v>0</v>
-      </c>
-      <c r="IG115">
-        <v>0</v>
-      </c>
-      <c r="IH115">
-        <v>0</v>
-      </c>
-      <c r="II115">
-        <v>0</v>
-      </c>
-      <c r="IJ115">
-        <v>0</v>
-      </c>
     </row>
     <row r="116" spans="1:246">
       <c r="A116" t="s">
@@ -52659,28 +52146,28 @@
         <v>0</v>
       </c>
       <c r="IE116">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="IF116">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="IG116">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="IH116">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="II116">
-        <v>104</v>
+        <v>2</v>
       </c>
       <c r="IJ116">
         <v>88</v>
       </c>
       <c r="IK116">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IL116">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:246">
@@ -53108,28 +52595,28 @@
         <v>0</v>
       </c>
       <c r="IE117">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="IF117">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="IG117">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH117">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="II117">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="IJ117">
         <v>160</v>
       </c>
       <c r="IK117">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="IL117">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:246">
@@ -53557,25 +53044,25 @@
         <v>0</v>
       </c>
       <c r="IE118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IF118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IG118">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH118">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="II118">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="IJ118">
         <v>23</v>
       </c>
       <c r="IK118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IL118">
         <v>0</v>
@@ -54006,28 +53493,28 @@
         <v>0</v>
       </c>
       <c r="IE119">
-        <v>4</v>
+        <v>0.75</v>
       </c>
       <c r="IF119">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="IG119">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="IH119">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="II119">
-        <v>69</v>
+        <v>2</v>
       </c>
       <c r="IJ119">
         <v>15</v>
       </c>
       <c r="IK119">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="IL119">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:246">
@@ -54455,28 +53942,28 @@
         <v>0</v>
       </c>
       <c r="IE120">
-        <v>4</v>
+        <v>0.75</v>
       </c>
       <c r="IF120">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="IG120">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="IH120">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="II120">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="IJ120">
         <v>64</v>
       </c>
       <c r="IK120">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="IL120">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:246">
@@ -54904,28 +54391,28 @@
         <v>0</v>
       </c>
       <c r="IE121">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="IF121">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="IG121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH121">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="II121">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="IJ121">
         <v>43</v>
       </c>
       <c r="IK121">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="IL121">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:246">
@@ -55329,22 +54816,13 @@
         <v>0</v>
       </c>
       <c r="IE122">
-        <v>3</v>
-      </c>
-      <c r="IF122">
         <v>0</v>
       </c>
       <c r="IG122">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="IH122">
-        <v>0</v>
-      </c>
-      <c r="II122">
         <v>64</v>
-      </c>
-      <c r="IJ122">
-        <v>0</v>
       </c>
       <c r="IK122">
         <v>0</v>
@@ -55751,25 +55229,16 @@
         <v>0</v>
       </c>
       <c r="IE123">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="IG123">
         <v>6</v>
       </c>
-      <c r="IF123">
-        <v>0</v>
-      </c>
-      <c r="IG123">
-        <v>0</v>
-      </c>
       <c r="IH123">
-        <v>0</v>
-      </c>
-      <c r="II123">
         <v>164</v>
       </c>
-      <c r="IJ123">
-        <v>0</v>
-      </c>
       <c r="IK123">
-        <v>1.166666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:246">
@@ -56173,25 +55642,16 @@
         <v>0</v>
       </c>
       <c r="IE124">
-        <v>2</v>
-      </c>
-      <c r="IF124">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="IG124">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH124">
-        <v>0</v>
-      </c>
-      <c r="II124">
         <v>51</v>
       </c>
-      <c r="IJ124">
-        <v>0</v>
-      </c>
       <c r="IK124">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:246">
@@ -56616,22 +56076,22 @@
         <v>0</v>
       </c>
       <c r="ID125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IE125">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="IF125">
+        <v>0.8</v>
+      </c>
+      <c r="IG125">
+        <v>2</v>
+      </c>
+      <c r="IH125">
+        <v>12</v>
+      </c>
+      <c r="II125">
         <v>5</v>
-      </c>
-      <c r="IG125">
-        <v>0</v>
-      </c>
-      <c r="IH125">
-        <v>0</v>
-      </c>
-      <c r="II125">
-        <v>12</v>
       </c>
       <c r="IJ125">
         <v>170</v>
@@ -56640,7 +56100,7 @@
         <v>0</v>
       </c>
       <c r="IL125">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:246">
@@ -57068,28 +56528,28 @@
         <v>0</v>
       </c>
       <c r="IE126">
+        <v>0.2</v>
+      </c>
+      <c r="IF126">
+        <v>0.25</v>
+      </c>
+      <c r="IG126">
         <v>5</v>
       </c>
-      <c r="IF126">
-        <v>4</v>
-      </c>
-      <c r="IG126">
-        <v>0</v>
-      </c>
       <c r="IH126">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="II126">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="IJ126">
         <v>61</v>
       </c>
       <c r="IK126">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="IL126">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:246">
@@ -57517,19 +56977,19 @@
         <v>0</v>
       </c>
       <c r="IE127">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="IF127">
+        <v>0</v>
+      </c>
+      <c r="IG127">
+        <v>2</v>
+      </c>
+      <c r="IH127">
+        <v>67</v>
+      </c>
+      <c r="II127">
         <v>5</v>
-      </c>
-      <c r="IG127">
-        <v>0</v>
-      </c>
-      <c r="IH127">
-        <v>0</v>
-      </c>
-      <c r="II127">
-        <v>67</v>
       </c>
       <c r="IJ127">
         <v>57</v>
@@ -57954,25 +57414,25 @@
         <v>0</v>
       </c>
       <c r="IE128">
-        <v>3</v>
-      </c>
-      <c r="IF128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IG128">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="IH128">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="II128">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="IJ128">
         <v>0</v>
       </c>
       <c r="IK128">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="IL128">
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:246">
@@ -58373,7 +57833,7 @@
         <v>2</v>
       </c>
       <c r="HV129">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="HW129">
         <v>3</v>
@@ -58385,7 +57845,7 @@
         <v>1</v>
       </c>
       <c r="HZ129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IA129">
         <v>1</v>
@@ -58400,25 +57860,25 @@
         <v>0</v>
       </c>
       <c r="IE129">
-        <v>3</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="IF129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IG129">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="IH129">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="II129">
-        <v>134</v>
+        <v>1</v>
       </c>
       <c r="IJ129">
         <v>4</v>
       </c>
       <c r="IK129">
-        <v>1.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="IL129">
         <v>0</v>
@@ -58822,7 +58282,7 @@
         <v>2</v>
       </c>
       <c r="HV130">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="HW130">
         <v>3</v>
@@ -58834,7 +58294,7 @@
         <v>1</v>
       </c>
       <c r="HZ130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IA130">
         <v>1</v>
@@ -58849,28 +58309,28 @@
         <v>0</v>
       </c>
       <c r="IE130">
-        <v>3</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="IF130">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="IG130">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="IH130">
-        <v>0</v>
+        <v>377</v>
       </c>
       <c r="II130">
-        <v>377</v>
+        <v>2</v>
       </c>
       <c r="IJ130">
         <v>141</v>
       </c>
       <c r="IK130">
-        <v>1.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="IL130">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:246">
@@ -59280,25 +58740,16 @@
         <v>0</v>
       </c>
       <c r="IE131">
-        <v>1</v>
-      </c>
-      <c r="IF131">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IG131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH131">
-        <v>0</v>
-      </c>
-      <c r="II131">
         <v>12</v>
       </c>
-      <c r="IJ131">
-        <v>0</v>
-      </c>
       <c r="IK131">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:246">
@@ -59708,22 +59159,13 @@
         <v>0</v>
       </c>
       <c r="IE132">
-        <v>1</v>
-      </c>
-      <c r="IF132">
         <v>0</v>
       </c>
       <c r="IG132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH132">
-        <v>0</v>
-      </c>
-      <c r="II132">
         <v>37</v>
-      </c>
-      <c r="IJ132">
-        <v>0</v>
       </c>
       <c r="IK132">
         <v>0</v>
@@ -60136,25 +59578,16 @@
         <v>0</v>
       </c>
       <c r="IE133">
-        <v>2</v>
-      </c>
-      <c r="IF133">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="IG133">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH133">
-        <v>0</v>
-      </c>
-      <c r="II133">
         <v>146</v>
       </c>
-      <c r="IJ133">
-        <v>0</v>
-      </c>
       <c r="IK133">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:246">
@@ -60561,28 +59994,19 @@
         <v>0</v>
       </c>
       <c r="ID134">
-        <v>1</v>
-      </c>
-      <c r="IE134">
         <v>0</v>
       </c>
       <c r="IF134">
-        <v>2</v>
-      </c>
-      <c r="IG134">
-        <v>0</v>
-      </c>
-      <c r="IH134">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="II134">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IJ134">
         <v>103</v>
       </c>
       <c r="IL134">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:246">
@@ -60991,26 +60415,17 @@
       <c r="ID135">
         <v>0</v>
       </c>
-      <c r="IE135">
-        <v>0</v>
-      </c>
       <c r="IF135">
         <v>1</v>
       </c>
-      <c r="IG135">
-        <v>0</v>
-      </c>
-      <c r="IH135">
-        <v>0</v>
-      </c>
       <c r="II135">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IJ135">
         <v>12</v>
       </c>
       <c r="IL135">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:246">
@@ -61419,20 +60834,11 @@
       <c r="ID136">
         <v>0</v>
       </c>
-      <c r="IE136">
-        <v>0</v>
-      </c>
       <c r="IF136">
-        <v>1</v>
-      </c>
-      <c r="IG136">
-        <v>0</v>
-      </c>
-      <c r="IH136">
         <v>0</v>
       </c>
       <c r="II136">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IJ136">
         <v>17</v>
@@ -61823,24 +61229,6 @@
       <c r="ID137">
         <v>0</v>
       </c>
-      <c r="IE137">
-        <v>0</v>
-      </c>
-      <c r="IF137">
-        <v>0</v>
-      </c>
-      <c r="IG137">
-        <v>0</v>
-      </c>
-      <c r="IH137">
-        <v>0</v>
-      </c>
-      <c r="II137">
-        <v>0</v>
-      </c>
-      <c r="IJ137">
-        <v>0</v>
-      </c>
     </row>
     <row r="138" spans="1:246">
       <c r="A138" t="s">
@@ -62224,24 +61612,6 @@
       <c r="ID138">
         <v>0</v>
       </c>
-      <c r="IE138">
-        <v>0</v>
-      </c>
-      <c r="IF138">
-        <v>0</v>
-      </c>
-      <c r="IG138">
-        <v>0</v>
-      </c>
-      <c r="IH138">
-        <v>0</v>
-      </c>
-      <c r="II138">
-        <v>0</v>
-      </c>
-      <c r="IJ138">
-        <v>0</v>
-      </c>
     </row>
     <row r="139" spans="1:246">
       <c r="A139" t="s">
@@ -62625,24 +61995,6 @@
       <c r="ID139">
         <v>0</v>
       </c>
-      <c r="IE139">
-        <v>0</v>
-      </c>
-      <c r="IF139">
-        <v>0</v>
-      </c>
-      <c r="IG139">
-        <v>0</v>
-      </c>
-      <c r="IH139">
-        <v>0</v>
-      </c>
-      <c r="II139">
-        <v>0</v>
-      </c>
-      <c r="IJ139">
-        <v>0</v>
-      </c>
     </row>
     <row r="140" spans="1:246">
       <c r="A140" t="s">
@@ -63066,28 +62418,28 @@
         <v>0</v>
       </c>
       <c r="IE140">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="IF140">
-        <v>4</v>
+        <v>1.75</v>
       </c>
       <c r="IG140">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH140">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="II140">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="IJ140">
         <v>171</v>
       </c>
       <c r="IK140">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="IL140">
-        <v>1.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:246">
@@ -63512,19 +62864,19 @@
         <v>0</v>
       </c>
       <c r="IE141">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="IF141">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="IG141">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH141">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="II141">
-        <v>95</v>
+        <v>4</v>
       </c>
       <c r="IJ141">
         <v>145</v>
@@ -63533,7 +62885,7 @@
         <v>0</v>
       </c>
       <c r="IL141">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:246">
@@ -63955,31 +63307,31 @@
         <v>0</v>
       </c>
       <c r="ID142">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IE142">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="IF142">
+        <v>0</v>
+      </c>
+      <c r="IG142">
+        <v>2</v>
+      </c>
+      <c r="IH142">
+        <v>60</v>
+      </c>
+      <c r="II142">
         <v>8</v>
-      </c>
-      <c r="IG142">
-        <v>0</v>
-      </c>
-      <c r="IH142">
-        <v>0</v>
-      </c>
-      <c r="II142">
-        <v>60</v>
       </c>
       <c r="IJ142">
         <v>306</v>
       </c>
       <c r="IK142">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="IL142">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:246">
@@ -64404,19 +63756,19 @@
         <v>0</v>
       </c>
       <c r="IE143">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="IF143">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IG143">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH143">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="II143">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="IJ143">
         <v>57</v>
@@ -64425,7 +63777,7 @@
         <v>0</v>
       </c>
       <c r="IL143">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:246">
@@ -64847,22 +64199,22 @@
         <v>0</v>
       </c>
       <c r="ID144">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="IE144">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IF144">
+        <v>1.2</v>
+      </c>
+      <c r="IG144">
+        <v>1</v>
+      </c>
+      <c r="IH144">
+        <v>52</v>
+      </c>
+      <c r="II144">
         <v>5</v>
-      </c>
-      <c r="IG144">
-        <v>0</v>
-      </c>
-      <c r="IH144">
-        <v>0</v>
-      </c>
-      <c r="II144">
-        <v>52</v>
       </c>
       <c r="IJ144">
         <v>214</v>
@@ -64871,7 +64223,7 @@
         <v>0</v>
       </c>
       <c r="IL144">
-        <v>1.2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="145" spans="1:246">
@@ -65293,31 +64645,31 @@
         <v>0</v>
       </c>
       <c r="ID145">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IE145">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="IF145">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="IG145">
+        <v>4</v>
+      </c>
+      <c r="IH145">
+        <v>100</v>
+      </c>
+      <c r="II145">
         <v>7</v>
-      </c>
-      <c r="IG145">
-        <v>0</v>
-      </c>
-      <c r="IH145">
-        <v>0</v>
-      </c>
-      <c r="II145">
-        <v>100</v>
       </c>
       <c r="IJ145">
         <v>196</v>
       </c>
       <c r="IK145">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="IL145">
-        <v>0.1428571428571428</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:246">
@@ -65742,19 +65094,19 @@
         <v>0</v>
       </c>
       <c r="IE146">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="IF146">
-        <v>3</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="IG146">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH146">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="II146">
-        <v>76</v>
+        <v>3</v>
       </c>
       <c r="IJ146">
         <v>86</v>
@@ -65763,7 +65115,7 @@
         <v>0</v>
       </c>
       <c r="IL146">
-        <v>1.333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:246">
@@ -66188,19 +65540,19 @@
         <v>0</v>
       </c>
       <c r="IE147">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IF147">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="IG147">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH147">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="II147">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="IJ147">
         <v>117</v>
@@ -66209,7 +65561,7 @@
         <v>0</v>
       </c>
       <c r="IL147">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:246">
@@ -66631,31 +65983,31 @@
         <v>0</v>
       </c>
       <c r="ID148">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IE148">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="IF148">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="IG148">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="IH148">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="II148">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="IJ148">
         <v>218</v>
       </c>
       <c r="IK148">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IL148">
-        <v>2.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149" spans="1:246">
@@ -67083,28 +66435,28 @@
         <v>0</v>
       </c>
       <c r="IE149">
+        <v>0.5</v>
+      </c>
+      <c r="IF149">
+        <v>-0.25</v>
+      </c>
+      <c r="IG149">
         <v>8</v>
       </c>
-      <c r="IF149">
-        <v>4</v>
-      </c>
-      <c r="IG149">
-        <v>0</v>
-      </c>
       <c r="IH149">
-        <v>0</v>
+        <v>282</v>
       </c>
       <c r="II149">
-        <v>282</v>
+        <v>4</v>
       </c>
       <c r="IJ149">
         <v>35</v>
       </c>
       <c r="IK149">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="IL149">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:246">
@@ -67532,28 +66884,28 @@
         <v>0</v>
       </c>
       <c r="IE150">
+        <v>-0.8</v>
+      </c>
+      <c r="IF150">
+        <v>2.5</v>
+      </c>
+      <c r="IG150">
         <v>5</v>
       </c>
-      <c r="IF150">
-        <v>2</v>
-      </c>
-      <c r="IG150">
-        <v>0</v>
-      </c>
       <c r="IH150">
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="II150">
-        <v>273</v>
+        <v>2</v>
       </c>
       <c r="IJ150">
         <v>18</v>
       </c>
       <c r="IK150">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="IL150">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:246">
@@ -67981,19 +67333,19 @@
         <v>0</v>
       </c>
       <c r="IE151">
+        <v>0</v>
+      </c>
+      <c r="IF151">
+        <v>0.2</v>
+      </c>
+      <c r="IG151">
         <v>5</v>
       </c>
-      <c r="IF151">
+      <c r="IH151">
+        <v>110</v>
+      </c>
+      <c r="II151">
         <v>5</v>
-      </c>
-      <c r="IG151">
-        <v>0</v>
-      </c>
-      <c r="IH151">
-        <v>0</v>
-      </c>
-      <c r="II151">
-        <v>110</v>
       </c>
       <c r="IJ151">
         <v>132</v>
@@ -68002,7 +67354,7 @@
         <v>0</v>
       </c>
       <c r="IL151">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:246">
@@ -68390,22 +67742,13 @@
       <c r="ID152">
         <v>0</v>
       </c>
-      <c r="IE152">
-        <v>0</v>
-      </c>
-      <c r="IF152">
-        <v>0</v>
-      </c>
       <c r="IG152">
         <v>0</v>
       </c>
       <c r="IH152">
         <v>0</v>
       </c>
-      <c r="II152">
-        <v>0</v>
-      </c>
-      <c r="IJ152">
+      <c r="IK152">
         <v>0</v>
       </c>
     </row>
@@ -68809,23 +68152,14 @@
       <c r="IE153">
         <v>1</v>
       </c>
-      <c r="IF153">
-        <v>0</v>
-      </c>
       <c r="IG153">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH153">
-        <v>0</v>
-      </c>
-      <c r="II153">
         <v>83</v>
       </c>
-      <c r="IJ153">
-        <v>0</v>
-      </c>
       <c r="IK153">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:246">
@@ -69213,22 +68547,13 @@
       <c r="ID154">
         <v>0</v>
       </c>
-      <c r="IE154">
-        <v>0</v>
-      </c>
-      <c r="IF154">
-        <v>0</v>
-      </c>
       <c r="IG154">
         <v>0</v>
       </c>
       <c r="IH154">
         <v>0</v>
       </c>
-      <c r="II154">
-        <v>0</v>
-      </c>
-      <c r="IJ154">
+      <c r="IK154">
         <v>0</v>
       </c>
     </row>
@@ -69654,19 +68979,19 @@
         <v>0</v>
       </c>
       <c r="IE155">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="IF155">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IG155">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH155">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="II155">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="IJ155">
         <v>21</v>
@@ -70100,25 +69425,25 @@
         <v>0</v>
       </c>
       <c r="IE156">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="IF156">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IG156">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH156">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="II156">
-        <v>138</v>
+        <v>1</v>
       </c>
       <c r="IJ156">
         <v>38</v>
       </c>
       <c r="IK156">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="IL156">
         <v>0</v>
@@ -70521,12 +69846,6 @@
       <c r="ID157">
         <v>0</v>
       </c>
-      <c r="IE157">
-        <v>0</v>
-      </c>
-      <c r="IF157">
-        <v>0</v>
-      </c>
       <c r="IG157">
         <v>0</v>
       </c>
@@ -70537,6 +69856,12 @@
         <v>0</v>
       </c>
       <c r="IJ157">
+        <v>0</v>
+      </c>
+      <c r="IK157">
+        <v>0</v>
+      </c>
+      <c r="IL157">
         <v>0</v>
       </c>
     </row>
@@ -70998,25 +70323,25 @@
         <v>0</v>
       </c>
       <c r="IE158">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="IF158">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="IG158">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH158">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="II158">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c r="IJ158">
         <v>50</v>
       </c>
       <c r="IK158">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="IL158">
         <v>0</v>
@@ -71477,22 +70802,22 @@
         <v>0</v>
       </c>
       <c r="ID159">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IE159">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="IF159">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="IG159">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH159">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="II159">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="IJ159">
         <v>72</v>
@@ -71501,7 +70826,7 @@
         <v>0</v>
       </c>
       <c r="IL159">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160" spans="1:246">
@@ -71959,22 +71284,22 @@
         <v>0</v>
       </c>
       <c r="ID160">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IE160">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="IF160">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="IG160">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH160">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="II160">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="IJ160">
         <v>79</v>
@@ -71983,7 +71308,7 @@
         <v>0</v>
       </c>
       <c r="IL160">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161" spans="1:246">
@@ -72411,28 +71736,28 @@
         <v>0</v>
       </c>
       <c r="IE161">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="IF161">
+        <v>1.2</v>
+      </c>
+      <c r="IG161">
+        <v>3</v>
+      </c>
+      <c r="IH161">
+        <v>6</v>
+      </c>
+      <c r="II161">
         <v>7</v>
-      </c>
-      <c r="IG161">
-        <v>0</v>
-      </c>
-      <c r="IH161">
-        <v>0</v>
-      </c>
-      <c r="II161">
-        <v>6</v>
       </c>
       <c r="IJ161">
         <v>82</v>
       </c>
       <c r="IK161">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="IL161">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:246">
@@ -72860,28 +72185,28 @@
         <v>0</v>
       </c>
       <c r="IE162">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IF162">
+        <v>1.6</v>
+      </c>
+      <c r="IG162">
+        <v>2</v>
+      </c>
+      <c r="IH162">
+        <v>49</v>
+      </c>
+      <c r="II162">
         <v>5</v>
-      </c>
-      <c r="IG162">
-        <v>0</v>
-      </c>
-      <c r="IH162">
-        <v>0</v>
-      </c>
-      <c r="II162">
-        <v>49</v>
       </c>
       <c r="IJ162">
         <v>157</v>
       </c>
       <c r="IK162">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IL162">
-        <v>1.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:246">
@@ -73306,31 +72631,31 @@
         <v>0</v>
       </c>
       <c r="ID163">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IE163">
         <v>2</v>
       </c>
       <c r="IF163">
-        <v>4</v>
+        <v>0.75</v>
       </c>
       <c r="IG163">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH163">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="II163">
-        <v>129</v>
+        <v>4</v>
       </c>
       <c r="IJ163">
         <v>158</v>
       </c>
       <c r="IK163">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="IL163">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164" spans="1:246">
@@ -73730,12 +73055,6 @@
       <c r="ID164">
         <v>0</v>
       </c>
-      <c r="IE164">
-        <v>0</v>
-      </c>
-      <c r="IF164">
-        <v>0</v>
-      </c>
       <c r="IG164">
         <v>0</v>
       </c>
@@ -73746,6 +73065,12 @@
         <v>0</v>
       </c>
       <c r="IJ164">
+        <v>0</v>
+      </c>
+      <c r="IK164">
+        <v>0</v>
+      </c>
+      <c r="IL164">
         <v>0</v>
       </c>
     </row>
@@ -74171,19 +73496,19 @@
         <v>0</v>
       </c>
       <c r="IE165">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IF165">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IG165">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH165">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="II165">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="IJ165">
         <v>71</v>
@@ -74617,25 +73942,25 @@
         <v>0</v>
       </c>
       <c r="IE166">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="IF166">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IG166">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH166">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="II166">
-        <v>126</v>
+        <v>1</v>
       </c>
       <c r="IJ166">
         <v>18</v>
       </c>
       <c r="IK166">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="IL166">
         <v>0</v>
@@ -75060,31 +74385,31 @@
         <v>0</v>
       </c>
       <c r="ID167">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IE167">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="IF167">
+        <v>-0.2</v>
+      </c>
+      <c r="IG167">
         <v>14</v>
       </c>
-      <c r="IF167">
+      <c r="IH167">
+        <v>514</v>
+      </c>
+      <c r="II167">
         <v>10</v>
-      </c>
-      <c r="IG167">
-        <v>0</v>
-      </c>
-      <c r="IH167">
-        <v>0</v>
-      </c>
-      <c r="II167">
-        <v>514</v>
       </c>
       <c r="IJ167">
         <v>355</v>
       </c>
       <c r="IK167">
-        <v>0.6428571428571429</v>
+        <v>0</v>
       </c>
       <c r="IL167">
-        <v>-0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168" spans="1:246">
@@ -75509,28 +74834,28 @@
         <v>0</v>
       </c>
       <c r="IE168">
+        <v>1</v>
+      </c>
+      <c r="IF168">
+        <v>1.5</v>
+      </c>
+      <c r="IG168">
         <v>9</v>
       </c>
-      <c r="IF168">
+      <c r="IH168">
+        <v>215</v>
+      </c>
+      <c r="II168">
         <v>6</v>
-      </c>
-      <c r="IG168">
-        <v>0</v>
-      </c>
-      <c r="IH168">
-        <v>0</v>
-      </c>
-      <c r="II168">
-        <v>215</v>
       </c>
       <c r="IJ168">
         <v>111</v>
       </c>
       <c r="IK168">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IL168">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:246">
@@ -75955,28 +75280,28 @@
         <v>0</v>
       </c>
       <c r="IE169">
-        <v>4</v>
+        <v>0.75</v>
       </c>
       <c r="IF169">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="IG169">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="IH169">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="II169">
-        <v>110</v>
+        <v>3</v>
       </c>
       <c r="IJ169">
         <v>124</v>
       </c>
       <c r="IK169">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="IL169">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170" spans="1:246">
@@ -76401,28 +75726,28 @@
         <v>0</v>
       </c>
       <c r="IE170">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="IF170">
         <v>1</v>
       </c>
       <c r="IG170">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH170">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="II170">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="IJ170">
         <v>22</v>
       </c>
       <c r="IK170">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="IL170">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:246">
@@ -76847,19 +76172,19 @@
         <v>0</v>
       </c>
       <c r="IE171">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="IF171">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="IG171">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH171">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="II171">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="IJ171">
         <v>54</v>
@@ -76868,7 +76193,7 @@
         <v>0</v>
       </c>
       <c r="IL171">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:246">
@@ -77281,24 +76606,24 @@
         <v>0</v>
       </c>
       <c r="IE172">
-        <v>1</v>
-      </c>
-      <c r="IF172">
         <v>0</v>
       </c>
       <c r="IG172">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH172">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="II172">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="IJ172">
         <v>0</v>
       </c>
       <c r="IK172">
+        <v>0</v>
+      </c>
+      <c r="IL172">
         <v>0</v>
       </c>
     </row>
@@ -77700,25 +77025,16 @@
         <v>0</v>
       </c>
       <c r="IE173">
-        <v>1</v>
-      </c>
-      <c r="IF173">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IG173">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH173">
-        <v>0</v>
-      </c>
-      <c r="II173">
         <v>11</v>
       </c>
-      <c r="IJ173">
-        <v>0</v>
-      </c>
       <c r="IK173">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:246">
@@ -78119,22 +77435,13 @@
         <v>0</v>
       </c>
       <c r="IE174">
-        <v>1</v>
-      </c>
-      <c r="IF174">
         <v>0</v>
       </c>
       <c r="IG174">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH174">
-        <v>0</v>
-      </c>
-      <c r="II174">
         <v>31</v>
-      </c>
-      <c r="IJ174">
-        <v>0</v>
       </c>
       <c r="IK174">
         <v>0</v>
@@ -78540,23 +77847,14 @@
       <c r="IE175">
         <v>1</v>
       </c>
-      <c r="IF175">
-        <v>0</v>
-      </c>
       <c r="IG175">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH175">
-        <v>0</v>
-      </c>
-      <c r="II175">
-        <v>3</v>
-      </c>
-      <c r="IJ175">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="IK175">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:246">
@@ -78954,7 +78252,7 @@
         <v>4</v>
       </c>
       <c r="HV176">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="HW176">
         <v>2</v>
@@ -78966,7 +78264,7 @@
         <v>1</v>
       </c>
       <c r="HZ176">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IA176">
         <v>1</v>
@@ -78981,28 +78279,28 @@
         <v>0</v>
       </c>
       <c r="IE176">
-        <v>2</v>
+        <v>-0.5</v>
       </c>
       <c r="IF176">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="IG176">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH176">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="II176">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="IJ176">
         <v>10</v>
       </c>
       <c r="IK176">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="IL176">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:246">
@@ -79415,25 +78713,25 @@
         <v>0</v>
       </c>
       <c r="IE177">
-        <v>1</v>
-      </c>
-      <c r="IF177">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IG177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IH177">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="II177">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="IJ177">
         <v>0</v>
       </c>
       <c r="IK177">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="IL177">
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:246">
@@ -79831,7 +79129,7 @@
         <v>4</v>
       </c>
       <c r="HV178">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="HW178">
         <v>3</v>
@@ -79843,7 +79141,7 @@
         <v>1</v>
       </c>
       <c r="HZ178">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IA178">
         <v>1</v>
@@ -79858,28 +79156,28 @@
         <v>0</v>
       </c>
       <c r="IE178">
-        <v>3</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="IF178">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="IG178">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="IH178">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="II178">
-        <v>107</v>
+        <v>1</v>
       </c>
       <c r="IJ178">
         <v>107</v>
       </c>
       <c r="IK178">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="IL178">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:246">
@@ -80304,28 +79602,28 @@
         <v>0</v>
       </c>
       <c r="IE179">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IF179">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="IG179">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH179">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="II179">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="IJ179">
         <v>64</v>
       </c>
       <c r="IK179">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IL179">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:246">
@@ -80747,28 +80045,28 @@
         <v>0</v>
       </c>
       <c r="ID180">
+        <v>0</v>
+      </c>
+      <c r="IE180">
+        <v>-0.5</v>
+      </c>
+      <c r="IF180">
         <v>-1</v>
       </c>
-      <c r="IE180">
-        <v>2</v>
-      </c>
-      <c r="IF180">
-        <v>2</v>
-      </c>
       <c r="IG180">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH180">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="II180">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="IJ180">
         <v>146</v>
       </c>
       <c r="IK180">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="IL180">
         <v>-1</v>
@@ -81196,28 +80494,28 @@
         <v>0</v>
       </c>
       <c r="IE181">
-        <v>3</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="IF181">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="IG181">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="IH181">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="II181">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="IJ181">
         <v>17</v>
       </c>
       <c r="IK181">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="IL181">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:246">
@@ -81629,11 +80927,8 @@
       <c r="ID182">
         <v>0</v>
       </c>
-      <c r="IE182">
-        <v>0</v>
-      </c>
       <c r="IF182">
-        <v>3</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="IG182">
         <v>0</v>
@@ -81642,13 +80937,16 @@
         <v>0</v>
       </c>
       <c r="II182">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="IJ182">
         <v>57</v>
       </c>
+      <c r="IK182">
+        <v>0</v>
+      </c>
       <c r="IL182">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:246">
@@ -82061,25 +81359,25 @@
         <v>0</v>
       </c>
       <c r="IE183">
-        <v>2</v>
-      </c>
-      <c r="IF183">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="IG183">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IH183">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="II183">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="IJ183">
         <v>0</v>
       </c>
       <c r="IK183">
-        <v>-1.5</v>
+        <v>0</v>
+      </c>
+      <c r="IL183">
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:246">
@@ -82491,11 +81789,8 @@
       <c r="ID184">
         <v>0</v>
       </c>
-      <c r="IE184">
-        <v>0</v>
-      </c>
       <c r="IF184">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="IG184">
         <v>0</v>
@@ -82504,13 +81799,16 @@
         <v>0</v>
       </c>
       <c r="II184">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IJ184">
         <v>46</v>
       </c>
+      <c r="IK184">
+        <v>0</v>
+      </c>
       <c r="IL184">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/dataset2026.xlsx
+++ b/dataset2026.xlsx
@@ -4820,7 +4820,7 @@
         <v>-1</v>
       </c>
       <c r="HV6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="HX6">
         <v>6</v>
@@ -6065,7 +6065,7 @@
         <v>1</v>
       </c>
       <c r="HX9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="HZ9">
         <v>1</v>
@@ -8145,10 +8145,10 @@
         <v>-1</v>
       </c>
       <c r="HU14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HV14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW14">
         <v>2</v>
@@ -8594,10 +8594,10 @@
         <v>-1</v>
       </c>
       <c r="HU15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HV15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW15">
         <v>2</v>
@@ -9043,10 +9043,10 @@
         <v>-1</v>
       </c>
       <c r="HU16">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HV16">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW16">
         <v>2</v>
@@ -11027,7 +11027,7 @@
         <v>-1</v>
       </c>
       <c r="HU21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="HW21">
         <v>2</v>
@@ -13089,7 +13089,7 @@
         <v>2</v>
       </c>
       <c r="HV26">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW26">
         <v>3</v>
@@ -13538,7 +13538,7 @@
         <v>2</v>
       </c>
       <c r="HV27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW27">
         <v>3</v>
@@ -13987,7 +13987,7 @@
         <v>2</v>
       </c>
       <c r="HV28">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW28">
         <v>2</v>
@@ -14436,13 +14436,13 @@
         <v>2</v>
       </c>
       <c r="HV29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW29">
         <v>3</v>
       </c>
       <c r="HX29">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="HY29">
         <v>1</v>
@@ -14885,7 +14885,7 @@
         <v>2</v>
       </c>
       <c r="HV30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW30">
         <v>2</v>
@@ -15334,7 +15334,7 @@
         <v>2</v>
       </c>
       <c r="HV31">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW31">
         <v>4</v>
@@ -17100,7 +17100,7 @@
         <v>2</v>
       </c>
       <c r="HV35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW35">
         <v>2</v>
@@ -17549,7 +17549,7 @@
         <v>2</v>
       </c>
       <c r="HV36">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW36">
         <v>3</v>
@@ -17998,7 +17998,7 @@
         <v>2</v>
       </c>
       <c r="HV37">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW37">
         <v>2</v>
@@ -20015,7 +20015,7 @@
         <v>1</v>
       </c>
       <c r="HV42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="HW42">
         <v>3</v>
@@ -22242,10 +22242,10 @@
         <v>-1</v>
       </c>
       <c r="HU47">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="HV47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="HW47">
         <v>3</v>
@@ -22691,10 +22691,10 @@
         <v>-1</v>
       </c>
       <c r="HU48">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="HV48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="HW48">
         <v>2</v>
@@ -23140,7 +23140,7 @@
         <v>-1</v>
       </c>
       <c r="HU49">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="HW49">
         <v>2</v>
@@ -23577,7 +23577,7 @@
         <v>-1</v>
       </c>
       <c r="HU50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HV50">
         <v>3</v>
@@ -24023,7 +24023,7 @@
         <v>-1</v>
       </c>
       <c r="HU51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HV51">
         <v>3</v>
@@ -24469,7 +24469,7 @@
         <v>-1</v>
       </c>
       <c r="HU52">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HV52">
         <v>3</v>
@@ -24906,7 +24906,7 @@
         <v>2</v>
       </c>
       <c r="HW53">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="HY53">
         <v>1</v>
@@ -26145,7 +26145,7 @@
         <v>1</v>
       </c>
       <c r="HU56">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HV56">
         <v>2</v>
@@ -27022,7 +27022,7 @@
         <v>1</v>
       </c>
       <c r="HU58">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HV58">
         <v>2</v>
@@ -28809,7 +28809,7 @@
         <v>1</v>
       </c>
       <c r="HV62">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW62">
         <v>3</v>
@@ -29255,7 +29255,7 @@
         <v>1</v>
       </c>
       <c r="HV63">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW63">
         <v>4</v>
@@ -29701,7 +29701,7 @@
         <v>1</v>
       </c>
       <c r="HV64">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW64">
         <v>2</v>
@@ -31485,7 +31485,7 @@
         <v>3</v>
       </c>
       <c r="HV68">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW68">
         <v>3</v>
@@ -32362,13 +32362,13 @@
         <v>3</v>
       </c>
       <c r="HV70">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW70">
         <v>2</v>
       </c>
       <c r="HX70">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="HY70">
         <v>1</v>
@@ -32808,7 +32808,7 @@
         <v>2</v>
       </c>
       <c r="HV71">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW71">
         <v>6</v>
@@ -33254,7 +33254,7 @@
         <v>2</v>
       </c>
       <c r="HV72">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW72">
         <v>3</v>
@@ -33697,7 +33697,7 @@
         <v>0</v>
       </c>
       <c r="HV73">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW73">
         <v>2</v>
@@ -40308,7 +40308,7 @@
         <v>2</v>
       </c>
       <c r="HV89">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW89">
         <v>3</v>
@@ -40754,7 +40754,7 @@
         <v>2</v>
       </c>
       <c r="HV90">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW90">
         <v>3</v>
@@ -41200,7 +41200,7 @@
         <v>2</v>
       </c>
       <c r="HV91">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW91">
         <v>2</v>
@@ -41649,7 +41649,7 @@
         <v>1</v>
       </c>
       <c r="HV92">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW92">
         <v>3</v>
@@ -42098,7 +42098,7 @@
         <v>1</v>
       </c>
       <c r="HV93">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW93">
         <v>2</v>
@@ -42547,7 +42547,7 @@
         <v>1</v>
       </c>
       <c r="HV94">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW94">
         <v>2</v>
@@ -44328,7 +44328,7 @@
         <v>-1</v>
       </c>
       <c r="HU98">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW98">
         <v>2</v>
@@ -44741,7 +44741,7 @@
         <v>-1</v>
       </c>
       <c r="HU99">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW99">
         <v>4</v>
@@ -45154,7 +45154,7 @@
         <v>-1</v>
       </c>
       <c r="HU100">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW100">
         <v>2</v>
@@ -45579,10 +45579,10 @@
         <v>0</v>
       </c>
       <c r="HU101">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HV101">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW101">
         <v>2</v>
@@ -46028,10 +46028,10 @@
         <v>1</v>
       </c>
       <c r="HU102">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HV102">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW102">
         <v>3</v>
@@ -46477,10 +46477,10 @@
         <v>1</v>
       </c>
       <c r="HU103">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HV103">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW103">
         <v>2</v>
@@ -46929,7 +46929,7 @@
         <v>2</v>
       </c>
       <c r="HV104">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW104">
         <v>3</v>
@@ -47378,7 +47378,7 @@
         <v>2</v>
       </c>
       <c r="HV105">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW105">
         <v>2</v>
@@ -47827,7 +47827,7 @@
         <v>2</v>
       </c>
       <c r="HV106">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW106">
         <v>2</v>
@@ -48276,7 +48276,7 @@
         <v>2</v>
       </c>
       <c r="HV107">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW107">
         <v>2</v>
@@ -48725,7 +48725,7 @@
         <v>2</v>
       </c>
       <c r="HV108">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW108">
         <v>3</v>
@@ -49174,7 +49174,7 @@
         <v>2</v>
       </c>
       <c r="HV109">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW109">
         <v>3</v>
@@ -52119,7 +52119,7 @@
         <v>2</v>
       </c>
       <c r="HV116">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW116">
         <v>3</v>
@@ -52568,7 +52568,7 @@
         <v>2</v>
       </c>
       <c r="HV117">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW117">
         <v>2</v>
@@ -53017,7 +53017,7 @@
         <v>2</v>
       </c>
       <c r="HV118">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW118">
         <v>2</v>
@@ -53466,7 +53466,7 @@
         <v>2</v>
       </c>
       <c r="HV119">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW119">
         <v>3</v>
@@ -53915,7 +53915,7 @@
         <v>2</v>
       </c>
       <c r="HV120">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW120">
         <v>2</v>
@@ -54364,7 +54364,7 @@
         <v>2</v>
       </c>
       <c r="HV121">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW121">
         <v>1</v>
@@ -57833,7 +57833,7 @@
         <v>2</v>
       </c>
       <c r="HV129">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW129">
         <v>3</v>
@@ -58282,7 +58282,7 @@
         <v>2</v>
       </c>
       <c r="HV130">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW130">
         <v>3</v>
@@ -58722,7 +58722,7 @@
         <v>-1</v>
       </c>
       <c r="HU131">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW131">
         <v>2</v>
@@ -59141,7 +59141,7 @@
         <v>-1</v>
       </c>
       <c r="HU132">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW132">
         <v>2</v>
@@ -59560,10 +59560,10 @@
         <v>-1</v>
       </c>
       <c r="HU133">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW133">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="HY133">
         <v>1</v>
@@ -60401,7 +60401,7 @@
         <v>3</v>
       </c>
       <c r="HX135">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="HZ135">
         <v>1</v>
@@ -60820,7 +60820,7 @@
         <v>3</v>
       </c>
       <c r="HX136">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="HZ136">
         <v>1</v>
@@ -62388,7 +62388,7 @@
         <v>1</v>
       </c>
       <c r="HU140">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HV140">
         <v>2</v>
@@ -62834,7 +62834,7 @@
         <v>1</v>
       </c>
       <c r="HU141">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HV141">
         <v>2</v>
@@ -63280,7 +63280,7 @@
         <v>0</v>
       </c>
       <c r="HU142">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HV142">
         <v>2</v>
@@ -65064,10 +65064,10 @@
         <v>-1</v>
       </c>
       <c r="HU146">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HV146">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW146">
         <v>3</v>
@@ -65510,10 +65510,10 @@
         <v>-1</v>
       </c>
       <c r="HU147">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HV147">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW147">
         <v>2</v>
@@ -65956,10 +65956,10 @@
         <v>-1</v>
       </c>
       <c r="HU148">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HV148">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW148">
         <v>2</v>
@@ -68952,10 +68952,10 @@
         <v>3</v>
       </c>
       <c r="HV155">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW155">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="HX155">
         <v>2</v>
@@ -69398,7 +69398,7 @@
         <v>3</v>
       </c>
       <c r="HV156">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW156">
         <v>3</v>
@@ -70296,10 +70296,10 @@
         <v>3</v>
       </c>
       <c r="HV158">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW158">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="HX158">
         <v>3</v>
@@ -70778,7 +70778,7 @@
         <v>3</v>
       </c>
       <c r="HV159">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW159">
         <v>2</v>
@@ -71260,7 +71260,7 @@
         <v>3</v>
       </c>
       <c r="HV160">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW160">
         <v>2</v>
@@ -74361,10 +74361,10 @@
         <v>2</v>
       </c>
       <c r="HV167">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW167">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="HX167">
         <v>1</v>
@@ -74807,7 +74807,7 @@
         <v>2</v>
       </c>
       <c r="HV168">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW168">
         <v>2</v>
@@ -75253,7 +75253,7 @@
         <v>2</v>
       </c>
       <c r="HV169">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW169">
         <v>2</v>
@@ -75699,7 +75699,7 @@
         <v>3</v>
       </c>
       <c r="HV170">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="HW170">
         <v>2</v>
@@ -76145,7 +76145,7 @@
         <v>3</v>
       </c>
       <c r="HV171">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="HW171">
         <v>3</v>
@@ -78249,10 +78249,10 @@
         <v>1</v>
       </c>
       <c r="HU176">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HV176">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW176">
         <v>2</v>
@@ -78695,7 +78695,7 @@
         <v>0</v>
       </c>
       <c r="HU177">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW177">
         <v>2</v>
@@ -79126,10 +79126,10 @@
         <v>1</v>
       </c>
       <c r="HU178">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HV178">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW178">
         <v>3</v>
@@ -79575,7 +79575,7 @@
         <v>2</v>
       </c>
       <c r="HV179">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW179">
         <v>2</v>
@@ -80021,7 +80021,7 @@
         <v>2</v>
       </c>
       <c r="HV180">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW180">
         <v>6</v>
@@ -80467,7 +80467,7 @@
         <v>2</v>
       </c>
       <c r="HV181">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HW181">
         <v>3</v>
@@ -80910,7 +80910,7 @@
         <v>-1</v>
       </c>
       <c r="HV182">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HX182">
         <v>3</v>
@@ -81772,7 +81772,7 @@
         <v>-1</v>
       </c>
       <c r="HV184">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="HX184">
         <v>2</v>

--- a/dataset2026.xlsx
+++ b/dataset2026.xlsx
@@ -784,12 +784,6 @@
     <t>chat_type2</t>
   </si>
   <si>
-    <t>individual_type1</t>
-  </si>
-  <si>
-    <t>individual_type2</t>
-  </si>
-  <si>
     <t>third_party_group1</t>
   </si>
   <si>
@@ -806,6 +800,12 @@
   </si>
   <si>
     <t>discuss2</t>
+  </si>
+  <si>
+    <t>individual_type1</t>
+  </si>
+  <si>
+    <t>individual_type2</t>
   </si>
   <si>
     <t>2023.12.14</t>
@@ -3330,19 +3330,19 @@
         <v>1</v>
       </c>
       <c r="IW2">
+        <v>1</v>
+      </c>
+      <c r="IY2">
+        <v>1</v>
+      </c>
+      <c r="JA2">
+        <v>1</v>
+      </c>
+      <c r="JB2">
+        <v>0</v>
+      </c>
+      <c r="JC2">
         <v>6</v>
-      </c>
-      <c r="IY2">
-        <v>1</v>
-      </c>
-      <c r="JA2">
-        <v>1</v>
-      </c>
-      <c r="JC2">
-        <v>1</v>
-      </c>
-      <c r="JD2">
-        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:264">
@@ -3779,7 +3779,7 @@
         <v>1</v>
       </c>
       <c r="IW3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY3">
         <v>1</v>
@@ -3787,11 +3787,11 @@
       <c r="JA3">
         <v>1</v>
       </c>
+      <c r="JB3">
+        <v>0</v>
+      </c>
       <c r="JC3">
-        <v>1</v>
-      </c>
-      <c r="JD3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:264">
@@ -4236,11 +4236,11 @@
       <c r="JA4">
         <v>1</v>
       </c>
+      <c r="JB4">
+        <v>0</v>
+      </c>
       <c r="JC4">
         <v>1</v>
-      </c>
-      <c r="JD4">
-        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:264">
@@ -4658,10 +4658,10 @@
       <c r="IN5">
         <v>2</v>
       </c>
-      <c r="JC5">
-        <v>0</v>
-      </c>
-      <c r="JD5">
+      <c r="JA5">
+        <v>0</v>
+      </c>
+      <c r="JB5">
         <v>0</v>
       </c>
     </row>
@@ -5105,19 +5105,19 @@
         <v>6</v>
       </c>
       <c r="IX6">
+        <v>1</v>
+      </c>
+      <c r="IZ6">
+        <v>1</v>
+      </c>
+      <c r="JA6">
+        <v>0</v>
+      </c>
+      <c r="JB6">
+        <v>1</v>
+      </c>
+      <c r="JD6">
         <v>7</v>
-      </c>
-      <c r="IZ6">
-        <v>1</v>
-      </c>
-      <c r="JB6">
-        <v>1</v>
-      </c>
-      <c r="JC6">
-        <v>0</v>
-      </c>
-      <c r="JD6">
-        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:264">
@@ -5535,10 +5535,10 @@
       <c r="IN7">
         <v>3</v>
       </c>
-      <c r="JC7">
-        <v>0</v>
-      </c>
-      <c r="JD7">
+      <c r="JA7">
+        <v>0</v>
+      </c>
+      <c r="JB7">
         <v>0</v>
       </c>
     </row>
@@ -5982,19 +5982,19 @@
         <v>3</v>
       </c>
       <c r="IX8">
+        <v>1</v>
+      </c>
+      <c r="IZ8">
+        <v>1</v>
+      </c>
+      <c r="JA8">
+        <v>0</v>
+      </c>
+      <c r="JB8">
+        <v>1</v>
+      </c>
+      <c r="JD8">
         <v>7</v>
-      </c>
-      <c r="IZ8">
-        <v>1</v>
-      </c>
-      <c r="JB8">
-        <v>1</v>
-      </c>
-      <c r="JC8">
-        <v>0</v>
-      </c>
-      <c r="JD8">
-        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:264">
@@ -6437,19 +6437,19 @@
         <v>3</v>
       </c>
       <c r="IX9">
+        <v>1</v>
+      </c>
+      <c r="IZ9">
+        <v>1</v>
+      </c>
+      <c r="JA9">
+        <v>0</v>
+      </c>
+      <c r="JB9">
+        <v>1</v>
+      </c>
+      <c r="JD9">
         <v>6</v>
-      </c>
-      <c r="IZ9">
-        <v>1</v>
-      </c>
-      <c r="JB9">
-        <v>1</v>
-      </c>
-      <c r="JC9">
-        <v>0</v>
-      </c>
-      <c r="JD9">
-        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:264">
@@ -6892,19 +6892,19 @@
         <v>3</v>
       </c>
       <c r="IX10">
+        <v>1</v>
+      </c>
+      <c r="IZ10">
+        <v>1</v>
+      </c>
+      <c r="JA10">
+        <v>0</v>
+      </c>
+      <c r="JB10">
+        <v>1</v>
+      </c>
+      <c r="JD10">
         <v>6</v>
-      </c>
-      <c r="IZ10">
-        <v>1</v>
-      </c>
-      <c r="JB10">
-        <v>1</v>
-      </c>
-      <c r="JC10">
-        <v>0</v>
-      </c>
-      <c r="JD10">
-        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:264">
@@ -7349,11 +7349,11 @@
       <c r="JA11">
         <v>1</v>
       </c>
+      <c r="JB11">
+        <v>0</v>
+      </c>
       <c r="JC11">
         <v>1</v>
-      </c>
-      <c r="JD11">
-        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:264">
@@ -7790,7 +7790,7 @@
         <v>1</v>
       </c>
       <c r="IW12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY12">
         <v>1</v>
@@ -7798,11 +7798,11 @@
       <c r="JA12">
         <v>1</v>
       </c>
+      <c r="JB12">
+        <v>0</v>
+      </c>
       <c r="JC12">
-        <v>1</v>
-      </c>
-      <c r="JD12">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:264">
@@ -8239,7 +8239,7 @@
         <v>1</v>
       </c>
       <c r="IW13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY13">
         <v>1</v>
@@ -8247,11 +8247,11 @@
       <c r="JA13">
         <v>1</v>
       </c>
+      <c r="JB13">
+        <v>0</v>
+      </c>
       <c r="JC13">
-        <v>1</v>
-      </c>
-      <c r="JD13">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:264">
@@ -8733,28 +8733,28 @@
         <v>5</v>
       </c>
       <c r="IW14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX14">
+        <v>1</v>
+      </c>
+      <c r="IY14">
+        <v>1</v>
+      </c>
+      <c r="IZ14">
+        <v>1</v>
+      </c>
+      <c r="JA14">
+        <v>1</v>
+      </c>
+      <c r="JB14">
+        <v>1</v>
+      </c>
+      <c r="JC14">
+        <v>2</v>
+      </c>
+      <c r="JD14">
         <v>7</v>
-      </c>
-      <c r="IY14">
-        <v>1</v>
-      </c>
-      <c r="IZ14">
-        <v>1</v>
-      </c>
-      <c r="JA14">
-        <v>1</v>
-      </c>
-      <c r="JB14">
-        <v>1</v>
-      </c>
-      <c r="JC14">
-        <v>1</v>
-      </c>
-      <c r="JD14">
-        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:264">
@@ -9236,10 +9236,10 @@
         <v>5</v>
       </c>
       <c r="IW15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY15">
         <v>1</v>
@@ -9254,10 +9254,10 @@
         <v>1</v>
       </c>
       <c r="JC15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:264">
@@ -9739,7 +9739,7 @@
         <v>5</v>
       </c>
       <c r="IW16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX16">
         <v>1</v>
@@ -9757,7 +9757,7 @@
         <v>1</v>
       </c>
       <c r="JC16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD16">
         <v>1</v>
@@ -10157,10 +10157,10 @@
       <c r="IN17">
         <v>2</v>
       </c>
-      <c r="JC17">
-        <v>0</v>
-      </c>
-      <c r="JD17">
+      <c r="JA17">
+        <v>0</v>
+      </c>
+      <c r="JB17">
         <v>0</v>
       </c>
     </row>
@@ -10558,10 +10558,10 @@
       <c r="IN18">
         <v>2</v>
       </c>
-      <c r="JC18">
-        <v>0</v>
-      </c>
-      <c r="JD18">
+      <c r="JA18">
+        <v>0</v>
+      </c>
+      <c r="JB18">
         <v>0</v>
       </c>
     </row>
@@ -10959,10 +10959,10 @@
       <c r="IN19">
         <v>2</v>
       </c>
-      <c r="JC19">
-        <v>0</v>
-      </c>
-      <c r="JD19">
+      <c r="JA19">
+        <v>0</v>
+      </c>
+      <c r="JB19">
         <v>0</v>
       </c>
     </row>
@@ -11375,10 +11375,10 @@
       <c r="IN20">
         <v>3</v>
       </c>
-      <c r="JC20">
-        <v>0</v>
-      </c>
-      <c r="JD20">
+      <c r="JA20">
+        <v>0</v>
+      </c>
+      <c r="JB20">
         <v>0</v>
       </c>
     </row>
@@ -11816,7 +11816,7 @@
         <v>6</v>
       </c>
       <c r="IW21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY21">
         <v>1</v>
@@ -11824,11 +11824,11 @@
       <c r="JA21">
         <v>1</v>
       </c>
+      <c r="JB21">
+        <v>0</v>
+      </c>
       <c r="JC21">
-        <v>1</v>
-      </c>
-      <c r="JD21">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:264">
@@ -12240,10 +12240,10 @@
       <c r="IN22">
         <v>2</v>
       </c>
-      <c r="JC22">
-        <v>0</v>
-      </c>
-      <c r="JD22">
+      <c r="JA22">
+        <v>0</v>
+      </c>
+      <c r="JB22">
         <v>0</v>
       </c>
     </row>
@@ -12678,7 +12678,7 @@
         <v>1</v>
       </c>
       <c r="IW23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="IY23">
         <v>1</v>
@@ -12686,11 +12686,11 @@
       <c r="JA23">
         <v>1</v>
       </c>
+      <c r="JB23">
+        <v>0</v>
+      </c>
       <c r="JC23">
-        <v>1</v>
-      </c>
-      <c r="JD23">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:264">
@@ -13127,7 +13127,7 @@
         <v>1</v>
       </c>
       <c r="IW24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY24">
         <v>1</v>
@@ -13135,11 +13135,11 @@
       <c r="JA24">
         <v>1</v>
       </c>
+      <c r="JB24">
+        <v>0</v>
+      </c>
       <c r="JC24">
-        <v>1</v>
-      </c>
-      <c r="JD24">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:264">
@@ -13576,19 +13576,19 @@
         <v>1</v>
       </c>
       <c r="IW25">
+        <v>1</v>
+      </c>
+      <c r="IY25">
+        <v>1</v>
+      </c>
+      <c r="JA25">
+        <v>1</v>
+      </c>
+      <c r="JB25">
+        <v>0</v>
+      </c>
+      <c r="JC25">
         <v>7</v>
-      </c>
-      <c r="IY25">
-        <v>1</v>
-      </c>
-      <c r="JA25">
-        <v>1</v>
-      </c>
-      <c r="JC25">
-        <v>1</v>
-      </c>
-      <c r="JD25">
-        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:264">
@@ -14576,7 +14576,7 @@
         <v>1</v>
       </c>
       <c r="IX27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY27">
         <v>1</v>
@@ -14594,7 +14594,7 @@
         <v>1</v>
       </c>
       <c r="JD27">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:264">
@@ -15076,10 +15076,10 @@
         <v>5</v>
       </c>
       <c r="IW28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY28">
         <v>1</v>
@@ -15094,10 +15094,10 @@
         <v>1</v>
       </c>
       <c r="JC28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD28">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:264">
@@ -15582,25 +15582,25 @@
         <v>1</v>
       </c>
       <c r="IX29">
+        <v>1</v>
+      </c>
+      <c r="IY29">
+        <v>1</v>
+      </c>
+      <c r="IZ29">
+        <v>1</v>
+      </c>
+      <c r="JA29">
+        <v>1</v>
+      </c>
+      <c r="JB29">
+        <v>1</v>
+      </c>
+      <c r="JC29">
+        <v>1</v>
+      </c>
+      <c r="JD29">
         <v>7</v>
-      </c>
-      <c r="IY29">
-        <v>1</v>
-      </c>
-      <c r="IZ29">
-        <v>1</v>
-      </c>
-      <c r="JA29">
-        <v>1</v>
-      </c>
-      <c r="JB29">
-        <v>1</v>
-      </c>
-      <c r="JC29">
-        <v>1</v>
-      </c>
-      <c r="JD29">
-        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:264">
@@ -16082,28 +16082,28 @@
         <v>3</v>
       </c>
       <c r="IW30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX30">
+        <v>1</v>
+      </c>
+      <c r="IY30">
+        <v>1</v>
+      </c>
+      <c r="IZ30">
+        <v>1</v>
+      </c>
+      <c r="JA30">
+        <v>1</v>
+      </c>
+      <c r="JB30">
+        <v>1</v>
+      </c>
+      <c r="JC30">
+        <v>2</v>
+      </c>
+      <c r="JD30">
         <v>7</v>
-      </c>
-      <c r="IY30">
-        <v>1</v>
-      </c>
-      <c r="IZ30">
-        <v>1</v>
-      </c>
-      <c r="JA30">
-        <v>1</v>
-      </c>
-      <c r="JB30">
-        <v>1</v>
-      </c>
-      <c r="JC30">
-        <v>1</v>
-      </c>
-      <c r="JD30">
-        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:264">
@@ -16585,28 +16585,28 @@
         <v>3</v>
       </c>
       <c r="IW31">
+        <v>1</v>
+      </c>
+      <c r="IX31">
+        <v>1</v>
+      </c>
+      <c r="IY31">
+        <v>1</v>
+      </c>
+      <c r="IZ31">
+        <v>1</v>
+      </c>
+      <c r="JA31">
+        <v>1</v>
+      </c>
+      <c r="JB31">
+        <v>1</v>
+      </c>
+      <c r="JC31">
         <v>6</v>
       </c>
-      <c r="IX31">
+      <c r="JD31">
         <v>6</v>
-      </c>
-      <c r="IY31">
-        <v>1</v>
-      </c>
-      <c r="IZ31">
-        <v>1</v>
-      </c>
-      <c r="JA31">
-        <v>1</v>
-      </c>
-      <c r="JB31">
-        <v>1</v>
-      </c>
-      <c r="JC31">
-        <v>1</v>
-      </c>
-      <c r="JD31">
-        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:264">
@@ -17088,28 +17088,28 @@
         <v>4</v>
       </c>
       <c r="IW32">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="IX32">
+        <v>0</v>
+      </c>
+      <c r="IY32">
+        <v>1</v>
+      </c>
+      <c r="IZ32">
+        <v>1</v>
+      </c>
+      <c r="JA32">
+        <v>1</v>
+      </c>
+      <c r="JB32">
+        <v>1</v>
+      </c>
+      <c r="JC32">
+        <v>4</v>
+      </c>
+      <c r="JD32">
         <v>6</v>
-      </c>
-      <c r="IY32">
-        <v>1</v>
-      </c>
-      <c r="IZ32">
-        <v>0</v>
-      </c>
-      <c r="JA32">
-        <v>1</v>
-      </c>
-      <c r="JB32">
-        <v>1</v>
-      </c>
-      <c r="JC32">
-        <v>1</v>
-      </c>
-      <c r="JD32">
-        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:264">
@@ -17542,10 +17542,10 @@
       <c r="IN33">
         <v>2</v>
       </c>
-      <c r="JC33">
-        <v>0</v>
-      </c>
-      <c r="JD33">
+      <c r="JA33">
+        <v>0</v>
+      </c>
+      <c r="JB33">
         <v>0</v>
       </c>
     </row>
@@ -18028,16 +18028,16 @@
         <v>4</v>
       </c>
       <c r="IW34">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="IX34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="IY34">
         <v>1</v>
       </c>
       <c r="IZ34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JA34">
         <v>1</v>
@@ -18046,10 +18046,10 @@
         <v>1</v>
       </c>
       <c r="JC34">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="JD34">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:264">
@@ -18531,10 +18531,10 @@
         <v>1</v>
       </c>
       <c r="IW35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY35">
         <v>1</v>
@@ -18549,10 +18549,10 @@
         <v>1</v>
       </c>
       <c r="JC35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD35">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:264">
@@ -19034,10 +19034,10 @@
         <v>1</v>
       </c>
       <c r="IW36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="IX36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="IY36">
         <v>1</v>
@@ -19052,10 +19052,10 @@
         <v>1</v>
       </c>
       <c r="JC36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="JD36">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:264">
@@ -19537,10 +19537,10 @@
         <v>1</v>
       </c>
       <c r="IW37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="IY37">
         <v>1</v>
@@ -19555,10 +19555,10 @@
         <v>1</v>
       </c>
       <c r="JC37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD37">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:264">
@@ -19955,10 +19955,10 @@
       <c r="IN38">
         <v>2</v>
       </c>
-      <c r="JC38">
-        <v>0</v>
-      </c>
-      <c r="JD38">
+      <c r="JA38">
+        <v>0</v>
+      </c>
+      <c r="JB38">
         <v>0</v>
       </c>
     </row>
@@ -20356,10 +20356,10 @@
       <c r="IN39">
         <v>2</v>
       </c>
-      <c r="JC39">
-        <v>0</v>
-      </c>
-      <c r="JD39">
+      <c r="JA39">
+        <v>0</v>
+      </c>
+      <c r="JB39">
         <v>0</v>
       </c>
     </row>
@@ -20757,10 +20757,10 @@
       <c r="IN40">
         <v>2</v>
       </c>
-      <c r="JC40">
-        <v>0</v>
-      </c>
-      <c r="JD40">
+      <c r="JA40">
+        <v>0</v>
+      </c>
+      <c r="JB40">
         <v>0</v>
       </c>
     </row>
@@ -21194,10 +21194,10 @@
       <c r="IN41">
         <v>2</v>
       </c>
-      <c r="JC41">
-        <v>0</v>
-      </c>
-      <c r="JD41">
+      <c r="JA41">
+        <v>0</v>
+      </c>
+      <c r="JB41">
         <v>0</v>
       </c>
     </row>
@@ -21680,28 +21680,28 @@
         <v>6</v>
       </c>
       <c r="IW42">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="IX42">
+        <v>1</v>
+      </c>
+      <c r="IY42">
+        <v>1</v>
+      </c>
+      <c r="IZ42">
+        <v>1</v>
+      </c>
+      <c r="JA42">
+        <v>1</v>
+      </c>
+      <c r="JB42">
+        <v>1</v>
+      </c>
+      <c r="JC42">
+        <v>4</v>
+      </c>
+      <c r="JD42">
         <v>5</v>
-      </c>
-      <c r="IY42">
-        <v>1</v>
-      </c>
-      <c r="IZ42">
-        <v>1</v>
-      </c>
-      <c r="JA42">
-        <v>1</v>
-      </c>
-      <c r="JB42">
-        <v>1</v>
-      </c>
-      <c r="JC42">
-        <v>1</v>
-      </c>
-      <c r="JD42">
-        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:264">
@@ -22159,7 +22159,7 @@
         <v>5</v>
       </c>
       <c r="IW43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY43">
         <v>1</v>
@@ -22167,11 +22167,11 @@
       <c r="JA43">
         <v>1</v>
       </c>
+      <c r="JB43">
+        <v>0</v>
+      </c>
       <c r="JC43">
-        <v>1</v>
-      </c>
-      <c r="JD43">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:264">
@@ -22653,10 +22653,10 @@
         <v>3</v>
       </c>
       <c r="IW44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="IX44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="IY44">
         <v>1</v>
@@ -22671,10 +22671,10 @@
         <v>1</v>
       </c>
       <c r="JC44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="JD44">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:264">
@@ -23156,10 +23156,10 @@
         <v>3</v>
       </c>
       <c r="IW45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY45">
         <v>1</v>
@@ -23174,10 +23174,10 @@
         <v>1</v>
       </c>
       <c r="JC45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD45">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:264">
@@ -23659,10 +23659,10 @@
         <v>3</v>
       </c>
       <c r="IW46">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="IX46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY46">
         <v>1</v>
@@ -23677,10 +23677,10 @@
         <v>1</v>
       </c>
       <c r="JC46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="JD46">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:264">
@@ -24162,28 +24162,28 @@
         <v>1</v>
       </c>
       <c r="IW47">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="IX47">
+        <v>1</v>
+      </c>
+      <c r="IY47">
+        <v>1</v>
+      </c>
+      <c r="IZ47">
+        <v>1</v>
+      </c>
+      <c r="JA47">
+        <v>1</v>
+      </c>
+      <c r="JB47">
+        <v>1</v>
+      </c>
+      <c r="JC47">
+        <v>3</v>
+      </c>
+      <c r="JD47">
         <v>5</v>
-      </c>
-      <c r="IY47">
-        <v>1</v>
-      </c>
-      <c r="IZ47">
-        <v>1</v>
-      </c>
-      <c r="JA47">
-        <v>1</v>
-      </c>
-      <c r="JB47">
-        <v>1</v>
-      </c>
-      <c r="JC47">
-        <v>1</v>
-      </c>
-      <c r="JD47">
-        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:264">
@@ -24665,10 +24665,10 @@
         <v>1</v>
       </c>
       <c r="IW48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="IY48">
         <v>1</v>
@@ -24683,10 +24683,10 @@
         <v>1</v>
       </c>
       <c r="JC48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD48">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:264">
@@ -25150,25 +25150,25 @@
         <v>3</v>
       </c>
       <c r="IW49">
-        <v>2</v>
-      </c>
-      <c r="IX49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY49">
         <v>1</v>
       </c>
+      <c r="IZ49">
+        <v>1</v>
+      </c>
       <c r="JA49">
         <v>1</v>
       </c>
       <c r="JB49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JC49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD49">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:264">
@@ -25647,7 +25647,7 @@
         <v>3</v>
       </c>
       <c r="IW50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX50">
         <v>1</v>
@@ -25665,7 +25665,7 @@
         <v>1</v>
       </c>
       <c r="JC50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD50">
         <v>1</v>
@@ -26147,10 +26147,10 @@
         <v>3</v>
       </c>
       <c r="IW51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY51">
         <v>1</v>
@@ -26165,10 +26165,10 @@
         <v>1</v>
       </c>
       <c r="JC51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD51">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:264">
@@ -26647,28 +26647,28 @@
         <v>3</v>
       </c>
       <c r="IW52">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="IX52">
+        <v>1</v>
+      </c>
+      <c r="IY52">
+        <v>1</v>
+      </c>
+      <c r="IZ52">
+        <v>1</v>
+      </c>
+      <c r="JA52">
+        <v>1</v>
+      </c>
+      <c r="JB52">
+        <v>1</v>
+      </c>
+      <c r="JC52">
+        <v>4</v>
+      </c>
+      <c r="JD52">
         <v>7</v>
-      </c>
-      <c r="IY52">
-        <v>1</v>
-      </c>
-      <c r="IZ52">
-        <v>1</v>
-      </c>
-      <c r="JA52">
-        <v>1</v>
-      </c>
-      <c r="JB52">
-        <v>1</v>
-      </c>
-      <c r="JC52">
-        <v>1</v>
-      </c>
-      <c r="JD52">
-        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:264">
@@ -27102,19 +27102,19 @@
         <v>3</v>
       </c>
       <c r="IW53">
+        <v>1</v>
+      </c>
+      <c r="IY53">
+        <v>1</v>
+      </c>
+      <c r="JA53">
+        <v>1</v>
+      </c>
+      <c r="JB53">
+        <v>0</v>
+      </c>
+      <c r="JC53">
         <v>7</v>
-      </c>
-      <c r="IY53">
-        <v>1</v>
-      </c>
-      <c r="JA53">
-        <v>1</v>
-      </c>
-      <c r="JC53">
-        <v>1</v>
-      </c>
-      <c r="JD53">
-        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:264">
@@ -27548,7 +27548,7 @@
         <v>3</v>
       </c>
       <c r="IW54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY54">
         <v>1</v>
@@ -27556,11 +27556,11 @@
       <c r="JA54">
         <v>1</v>
       </c>
+      <c r="JB54">
+        <v>0</v>
+      </c>
       <c r="JC54">
-        <v>1</v>
-      </c>
-      <c r="JD54">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:264">
@@ -27994,7 +27994,7 @@
         <v>3</v>
       </c>
       <c r="IW55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY55">
         <v>1</v>
@@ -28002,11 +28002,11 @@
       <c r="JA55">
         <v>1</v>
       </c>
+      <c r="JB55">
+        <v>0</v>
+      </c>
       <c r="JC55">
-        <v>1</v>
-      </c>
-      <c r="JD55">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:264">
@@ -28485,10 +28485,10 @@
         <v>1</v>
       </c>
       <c r="IW56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY56">
         <v>1</v>
@@ -28503,10 +28503,10 @@
         <v>1</v>
       </c>
       <c r="JC56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD56">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:264">
@@ -28961,19 +28961,19 @@
         <v>1</v>
       </c>
       <c r="IX57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IZ57">
         <v>1</v>
       </c>
+      <c r="JA57">
+        <v>0</v>
+      </c>
       <c r="JB57">
         <v>1</v>
       </c>
-      <c r="JC57">
-        <v>0</v>
-      </c>
       <c r="JD57">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:264">
@@ -29452,10 +29452,10 @@
         <v>1</v>
       </c>
       <c r="IW58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="IY58">
         <v>1</v>
@@ -29470,10 +29470,10 @@
         <v>1</v>
       </c>
       <c r="JC58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD58">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:264">
@@ -30452,10 +30452,10 @@
         <v>5</v>
       </c>
       <c r="IW60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY60">
         <v>1</v>
@@ -30470,10 +30470,10 @@
         <v>1</v>
       </c>
       <c r="JC60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD60">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:264">
@@ -30952,10 +30952,10 @@
         <v>5</v>
       </c>
       <c r="IW61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY61">
         <v>1</v>
@@ -30970,10 +30970,10 @@
         <v>1</v>
       </c>
       <c r="JC61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD61">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:264">
@@ -31952,28 +31952,28 @@
         <v>4</v>
       </c>
       <c r="IW63">
+        <v>1</v>
+      </c>
+      <c r="IX63">
+        <v>1</v>
+      </c>
+      <c r="IY63">
+        <v>1</v>
+      </c>
+      <c r="IZ63">
+        <v>1</v>
+      </c>
+      <c r="JA63">
+        <v>1</v>
+      </c>
+      <c r="JB63">
+        <v>1</v>
+      </c>
+      <c r="JC63">
         <v>6</v>
       </c>
-      <c r="IX63">
+      <c r="JD63">
         <v>6</v>
-      </c>
-      <c r="IY63">
-        <v>1</v>
-      </c>
-      <c r="IZ63">
-        <v>1</v>
-      </c>
-      <c r="JA63">
-        <v>1</v>
-      </c>
-      <c r="JB63">
-        <v>1</v>
-      </c>
-      <c r="JC63">
-        <v>1</v>
-      </c>
-      <c r="JD63">
-        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:264">
@@ -32452,10 +32452,10 @@
         <v>4</v>
       </c>
       <c r="IW64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY64">
         <v>1</v>
@@ -32470,10 +32470,10 @@
         <v>1</v>
       </c>
       <c r="JC64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD64">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:264">
@@ -32952,28 +32952,28 @@
         <v>1</v>
       </c>
       <c r="IW65">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="IX65">
+        <v>1</v>
+      </c>
+      <c r="IY65">
+        <v>1</v>
+      </c>
+      <c r="IZ65">
+        <v>1</v>
+      </c>
+      <c r="JA65">
+        <v>1</v>
+      </c>
+      <c r="JB65">
+        <v>1</v>
+      </c>
+      <c r="JC65">
+        <v>4</v>
+      </c>
+      <c r="JD65">
         <v>7</v>
-      </c>
-      <c r="IY65">
-        <v>1</v>
-      </c>
-      <c r="IZ65">
-        <v>1</v>
-      </c>
-      <c r="JA65">
-        <v>1</v>
-      </c>
-      <c r="JB65">
-        <v>1</v>
-      </c>
-      <c r="JC65">
-        <v>1</v>
-      </c>
-      <c r="JD65">
-        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:264">
@@ -33452,10 +33452,10 @@
         <v>1</v>
       </c>
       <c r="IW66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY66">
         <v>1</v>
@@ -33470,10 +33470,10 @@
         <v>1</v>
       </c>
       <c r="JC66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD66">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:264">
@@ -33952,25 +33952,25 @@
         <v>1</v>
       </c>
       <c r="IW67">
+        <v>1</v>
+      </c>
+      <c r="IX67">
+        <v>1</v>
+      </c>
+      <c r="IY67">
+        <v>1</v>
+      </c>
+      <c r="IZ67">
+        <v>1</v>
+      </c>
+      <c r="JA67">
+        <v>1</v>
+      </c>
+      <c r="JB67">
+        <v>1</v>
+      </c>
+      <c r="JC67">
         <v>5</v>
-      </c>
-      <c r="IX67">
-        <v>1</v>
-      </c>
-      <c r="IY67">
-        <v>1</v>
-      </c>
-      <c r="IZ67">
-        <v>1</v>
-      </c>
-      <c r="JA67">
-        <v>1</v>
-      </c>
-      <c r="JB67">
-        <v>1</v>
-      </c>
-      <c r="JC67">
-        <v>1</v>
       </c>
       <c r="JD67">
         <v>1</v>
@@ -34455,25 +34455,25 @@
         <v>1</v>
       </c>
       <c r="IX68">
+        <v>1</v>
+      </c>
+      <c r="IY68">
+        <v>1</v>
+      </c>
+      <c r="IZ68">
+        <v>1</v>
+      </c>
+      <c r="JA68">
+        <v>1</v>
+      </c>
+      <c r="JB68">
+        <v>1</v>
+      </c>
+      <c r="JC68">
+        <v>1</v>
+      </c>
+      <c r="JD68">
         <v>7</v>
-      </c>
-      <c r="IY68">
-        <v>1</v>
-      </c>
-      <c r="IZ68">
-        <v>1</v>
-      </c>
-      <c r="JA68">
-        <v>1</v>
-      </c>
-      <c r="JB68">
-        <v>1</v>
-      </c>
-      <c r="JC68">
-        <v>1</v>
-      </c>
-      <c r="JD68">
-        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:264">
@@ -34928,7 +34928,7 @@
         <v>2</v>
       </c>
       <c r="IW69">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="IY69">
         <v>1</v>
@@ -34936,11 +34936,11 @@
       <c r="JA69">
         <v>1</v>
       </c>
+      <c r="JB69">
+        <v>0</v>
+      </c>
       <c r="JC69">
         <v>1</v>
-      </c>
-      <c r="JD69">
-        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:264">
@@ -35419,10 +35419,10 @@
         <v>1</v>
       </c>
       <c r="IW70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY70">
         <v>1</v>
@@ -35437,10 +35437,10 @@
         <v>1</v>
       </c>
       <c r="JC70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD70">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:264">
@@ -35919,28 +35919,28 @@
         <v>1</v>
       </c>
       <c r="IW71">
+        <v>1</v>
+      </c>
+      <c r="IX71">
+        <v>1</v>
+      </c>
+      <c r="IY71">
+        <v>1</v>
+      </c>
+      <c r="IZ71">
+        <v>1</v>
+      </c>
+      <c r="JA71">
+        <v>1</v>
+      </c>
+      <c r="JB71">
+        <v>1</v>
+      </c>
+      <c r="JC71">
         <v>7</v>
       </c>
-      <c r="IX71">
-        <v>2</v>
-      </c>
-      <c r="IY71">
-        <v>1</v>
-      </c>
-      <c r="IZ71">
-        <v>1</v>
-      </c>
-      <c r="JA71">
-        <v>1</v>
-      </c>
-      <c r="JB71">
-        <v>1</v>
-      </c>
-      <c r="JC71">
-        <v>1</v>
-      </c>
       <c r="JD71">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:264">
@@ -36900,26 +36900,26 @@
       <c r="IV73">
         <v>1</v>
       </c>
-      <c r="IW73">
-        <v>2</v>
-      </c>
       <c r="IX73">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="IY73">
+        <v>1</v>
       </c>
       <c r="IZ73">
         <v>1</v>
       </c>
       <c r="JA73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73">
         <v>1</v>
       </c>
       <c r="JC73">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="JD73">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:264">
@@ -37313,10 +37313,10 @@
       <c r="IN74">
         <v>2</v>
       </c>
-      <c r="JC74">
-        <v>0</v>
-      </c>
-      <c r="JD74">
+      <c r="JA74">
+        <v>0</v>
+      </c>
+      <c r="JB74">
         <v>0</v>
       </c>
     </row>
@@ -37711,10 +37711,10 @@
       <c r="IN75">
         <v>2</v>
       </c>
-      <c r="JC75">
-        <v>0</v>
-      </c>
-      <c r="JD75">
+      <c r="JA75">
+        <v>0</v>
+      </c>
+      <c r="JB75">
         <v>0</v>
       </c>
     </row>
@@ -38109,10 +38109,10 @@
       <c r="IN76">
         <v>2</v>
       </c>
-      <c r="JC76">
-        <v>0</v>
-      </c>
-      <c r="JD76">
+      <c r="JA76">
+        <v>0</v>
+      </c>
+      <c r="JB76">
         <v>0</v>
       </c>
     </row>
@@ -39095,7 +39095,7 @@
         <v>1</v>
       </c>
       <c r="IX78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY78">
         <v>1</v>
@@ -39113,7 +39113,7 @@
         <v>1</v>
       </c>
       <c r="JD78">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:264">
@@ -39592,10 +39592,10 @@
         <v>3</v>
       </c>
       <c r="IW79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY79">
         <v>1</v>
@@ -39610,10 +39610,10 @@
         <v>1</v>
       </c>
       <c r="JC79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD79">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:264">
@@ -40092,28 +40092,28 @@
         <v>3</v>
       </c>
       <c r="IW80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX80">
+        <v>1</v>
+      </c>
+      <c r="IY80">
+        <v>1</v>
+      </c>
+      <c r="IZ80">
+        <v>1</v>
+      </c>
+      <c r="JA80">
+        <v>1</v>
+      </c>
+      <c r="JB80">
+        <v>1</v>
+      </c>
+      <c r="JC80">
+        <v>2</v>
+      </c>
+      <c r="JD80">
         <v>7</v>
-      </c>
-      <c r="IY80">
-        <v>1</v>
-      </c>
-      <c r="IZ80">
-        <v>1</v>
-      </c>
-      <c r="JA80">
-        <v>1</v>
-      </c>
-      <c r="JB80">
-        <v>1</v>
-      </c>
-      <c r="JC80">
-        <v>1</v>
-      </c>
-      <c r="JD80">
-        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:264">
@@ -40592,28 +40592,28 @@
         <v>3</v>
       </c>
       <c r="IW81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX81">
+        <v>1</v>
+      </c>
+      <c r="IY81">
+        <v>1</v>
+      </c>
+      <c r="IZ81">
+        <v>1</v>
+      </c>
+      <c r="JA81">
+        <v>1</v>
+      </c>
+      <c r="JB81">
+        <v>1</v>
+      </c>
+      <c r="JC81">
+        <v>2</v>
+      </c>
+      <c r="JD81">
         <v>6</v>
-      </c>
-      <c r="IY81">
-        <v>1</v>
-      </c>
-      <c r="IZ81">
-        <v>1</v>
-      </c>
-      <c r="JA81">
-        <v>1</v>
-      </c>
-      <c r="JB81">
-        <v>1</v>
-      </c>
-      <c r="JC81">
-        <v>1</v>
-      </c>
-      <c r="JD81">
-        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:264">
@@ -41092,10 +41092,10 @@
         <v>3</v>
       </c>
       <c r="IW82">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="IX82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY82">
         <v>1</v>
@@ -41110,10 +41110,10 @@
         <v>1</v>
       </c>
       <c r="JC82">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="JD82">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:264">
@@ -41507,10 +41507,10 @@
       <c r="IN83">
         <v>3</v>
       </c>
-      <c r="JC83">
-        <v>0</v>
-      </c>
-      <c r="JD83">
+      <c r="JA83">
+        <v>0</v>
+      </c>
+      <c r="JB83">
         <v>0</v>
       </c>
     </row>
@@ -41905,10 +41905,10 @@
       <c r="IN84">
         <v>2</v>
       </c>
-      <c r="JC84">
-        <v>0</v>
-      </c>
-      <c r="JD84">
+      <c r="JA84">
+        <v>0</v>
+      </c>
+      <c r="JB84">
         <v>0</v>
       </c>
     </row>
@@ -42303,10 +42303,10 @@
       <c r="IN85">
         <v>2</v>
       </c>
-      <c r="JC85">
-        <v>0</v>
-      </c>
-      <c r="JD85">
+      <c r="JA85">
+        <v>0</v>
+      </c>
+      <c r="JB85">
         <v>0</v>
       </c>
     </row>
@@ -42741,7 +42741,7 @@
         <v>5</v>
       </c>
       <c r="IW86">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="IY86">
         <v>1</v>
@@ -42749,11 +42749,11 @@
       <c r="JA86">
         <v>1</v>
       </c>
+      <c r="JB86">
+        <v>0</v>
+      </c>
       <c r="JC86">
-        <v>1</v>
-      </c>
-      <c r="JD86">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87" spans="1:264">
@@ -43187,19 +43187,19 @@
         <v>5</v>
       </c>
       <c r="IW87">
+        <v>1</v>
+      </c>
+      <c r="IY87">
+        <v>1</v>
+      </c>
+      <c r="JA87">
+        <v>1</v>
+      </c>
+      <c r="JB87">
+        <v>0</v>
+      </c>
+      <c r="JC87">
         <v>7</v>
-      </c>
-      <c r="IY87">
-        <v>1</v>
-      </c>
-      <c r="JA87">
-        <v>1</v>
-      </c>
-      <c r="JC87">
-        <v>1</v>
-      </c>
-      <c r="JD87">
-        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:264">
@@ -43608,10 +43608,10 @@
       <c r="IN88">
         <v>3</v>
       </c>
-      <c r="JC88">
-        <v>0</v>
-      </c>
-      <c r="JD88">
+      <c r="JA88">
+        <v>0</v>
+      </c>
+      <c r="JB88">
         <v>0</v>
       </c>
     </row>
@@ -44094,25 +44094,25 @@
         <v>1</v>
       </c>
       <c r="IX89">
+        <v>1</v>
+      </c>
+      <c r="IY89">
+        <v>1</v>
+      </c>
+      <c r="IZ89">
+        <v>1</v>
+      </c>
+      <c r="JA89">
+        <v>1</v>
+      </c>
+      <c r="JB89">
+        <v>1</v>
+      </c>
+      <c r="JC89">
+        <v>1</v>
+      </c>
+      <c r="JD89">
         <v>7</v>
-      </c>
-      <c r="IY89">
-        <v>1</v>
-      </c>
-      <c r="IZ89">
-        <v>1</v>
-      </c>
-      <c r="JA89">
-        <v>1</v>
-      </c>
-      <c r="JB89">
-        <v>1</v>
-      </c>
-      <c r="JC89">
-        <v>1</v>
-      </c>
-      <c r="JD89">
-        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:264">
@@ -44594,7 +44594,7 @@
         <v>1</v>
       </c>
       <c r="IX90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY90">
         <v>1</v>
@@ -44612,7 +44612,7 @@
         <v>1</v>
       </c>
       <c r="JD90">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91" spans="1:264">
@@ -45091,7 +45091,7 @@
         <v>5</v>
       </c>
       <c r="IW91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX91">
         <v>1</v>
@@ -45109,7 +45109,7 @@
         <v>1</v>
       </c>
       <c r="JC91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD91">
         <v>1</v>
@@ -46097,10 +46097,10 @@
         <v>2</v>
       </c>
       <c r="IW93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY93">
         <v>1</v>
@@ -46115,10 +46115,10 @@
         <v>1</v>
       </c>
       <c r="JC93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD93">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:264">
@@ -46600,7 +46600,7 @@
         <v>2</v>
       </c>
       <c r="IW94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX94">
         <v>1</v>
@@ -46618,7 +46618,7 @@
         <v>1</v>
       </c>
       <c r="JC94">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD94">
         <v>1</v>
@@ -47103,10 +47103,10 @@
         <v>1</v>
       </c>
       <c r="IW95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY95">
         <v>1</v>
@@ -47121,10 +47121,10 @@
         <v>1</v>
       </c>
       <c r="JC95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD95">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96" spans="1:264">
@@ -47606,7 +47606,7 @@
         <v>1</v>
       </c>
       <c r="IW96">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="IX96">
         <v>1</v>
@@ -47624,7 +47624,7 @@
         <v>1</v>
       </c>
       <c r="JC96">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="JD96">
         <v>1</v>
@@ -48109,10 +48109,10 @@
         <v>1</v>
       </c>
       <c r="IW97">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="IX97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY97">
         <v>1</v>
@@ -48127,10 +48127,10 @@
         <v>1</v>
       </c>
       <c r="JC97">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="JD97">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98" spans="1:264">
@@ -48567,7 +48567,7 @@
         <v>1</v>
       </c>
       <c r="IW98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY98">
         <v>1</v>
@@ -48575,11 +48575,11 @@
       <c r="JA98">
         <v>1</v>
       </c>
+      <c r="JB98">
+        <v>0</v>
+      </c>
       <c r="JC98">
-        <v>1</v>
-      </c>
-      <c r="JD98">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99" spans="1:264">
@@ -49016,19 +49016,19 @@
         <v>1</v>
       </c>
       <c r="IW99">
+        <v>1</v>
+      </c>
+      <c r="IY99">
+        <v>1</v>
+      </c>
+      <c r="JA99">
+        <v>1</v>
+      </c>
+      <c r="JB99">
+        <v>0</v>
+      </c>
+      <c r="JC99">
         <v>6</v>
-      </c>
-      <c r="IY99">
-        <v>1</v>
-      </c>
-      <c r="JA99">
-        <v>1</v>
-      </c>
-      <c r="JC99">
-        <v>1</v>
-      </c>
-      <c r="JD99">
-        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:264">
@@ -49465,7 +49465,7 @@
         <v>1</v>
       </c>
       <c r="IW100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY100">
         <v>1</v>
@@ -49473,11 +49473,11 @@
       <c r="JA100">
         <v>1</v>
       </c>
+      <c r="JB100">
+        <v>0</v>
+      </c>
       <c r="JC100">
-        <v>1</v>
-      </c>
-      <c r="JD100">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101" spans="1:264">
@@ -49959,10 +49959,10 @@
         <v>4</v>
       </c>
       <c r="IW101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY101">
         <v>1</v>
@@ -49977,10 +49977,10 @@
         <v>1</v>
       </c>
       <c r="JC101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD101">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102" spans="1:264">
@@ -50462,10 +50462,10 @@
         <v>4</v>
       </c>
       <c r="IW102">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="IX102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY102">
         <v>1</v>
@@ -50480,10 +50480,10 @@
         <v>1</v>
       </c>
       <c r="JC102">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="JD102">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103" spans="1:264">
@@ -50965,7 +50965,7 @@
         <v>4</v>
       </c>
       <c r="IW103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX103">
         <v>1</v>
@@ -50983,7 +50983,7 @@
         <v>1</v>
       </c>
       <c r="JC103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD103">
         <v>1</v>
@@ -51468,7 +51468,7 @@
         <v>1</v>
       </c>
       <c r="IW104">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="IX104">
         <v>1</v>
@@ -51486,7 +51486,7 @@
         <v>1</v>
       </c>
       <c r="JC104">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="JD104">
         <v>1</v>
@@ -51971,10 +51971,10 @@
         <v>1</v>
       </c>
       <c r="IW105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY105">
         <v>1</v>
@@ -51989,10 +51989,10 @@
         <v>1</v>
       </c>
       <c r="JC105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD105">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106" spans="1:264">
@@ -52474,10 +52474,10 @@
         <v>1</v>
       </c>
       <c r="IW106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY106">
         <v>1</v>
@@ -52492,10 +52492,10 @@
         <v>1</v>
       </c>
       <c r="JC106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD106">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107" spans="1:264">
@@ -52977,10 +52977,10 @@
         <v>5</v>
       </c>
       <c r="IW107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY107">
         <v>1</v>
@@ -52995,10 +52995,10 @@
         <v>1</v>
       </c>
       <c r="JC107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD107">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108" spans="1:264">
@@ -53480,10 +53480,10 @@
         <v>5</v>
       </c>
       <c r="IW108">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="IX108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY108">
         <v>1</v>
@@ -53498,10 +53498,10 @@
         <v>1</v>
       </c>
       <c r="JC108">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="JD108">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109" spans="1:264">
@@ -53983,10 +53983,10 @@
         <v>5</v>
       </c>
       <c r="IW109">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="IX109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY109">
         <v>1</v>
@@ -54001,10 +54001,10 @@
         <v>1</v>
       </c>
       <c r="JC109">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="JD109">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110" spans="1:264">
@@ -54486,10 +54486,10 @@
         <v>4</v>
       </c>
       <c r="IW110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY110">
         <v>1</v>
@@ -54504,10 +54504,10 @@
         <v>1</v>
       </c>
       <c r="JC110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD110">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111" spans="1:264">
@@ -54989,10 +54989,10 @@
         <v>4</v>
       </c>
       <c r="IW111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY111">
         <v>1</v>
@@ -55007,10 +55007,10 @@
         <v>1</v>
       </c>
       <c r="JC111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD111">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112" spans="1:264">
@@ -55492,7 +55492,7 @@
         <v>4</v>
       </c>
       <c r="IW112">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="IX112">
         <v>1</v>
@@ -55510,7 +55510,7 @@
         <v>1</v>
       </c>
       <c r="JC112">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="JD112">
         <v>1</v>
@@ -55910,10 +55910,10 @@
       <c r="IN113">
         <v>2</v>
       </c>
-      <c r="JC113">
-        <v>0</v>
-      </c>
-      <c r="JD113">
+      <c r="JA113">
+        <v>0</v>
+      </c>
+      <c r="JB113">
         <v>0</v>
       </c>
     </row>
@@ -56311,10 +56311,10 @@
       <c r="IN114">
         <v>2</v>
       </c>
-      <c r="JC114">
-        <v>0</v>
-      </c>
-      <c r="JD114">
+      <c r="JA114">
+        <v>0</v>
+      </c>
+      <c r="JB114">
         <v>0</v>
       </c>
     </row>
@@ -56712,10 +56712,10 @@
       <c r="IN115">
         <v>2</v>
       </c>
-      <c r="JC115">
-        <v>0</v>
-      </c>
-      <c r="JD115">
+      <c r="JA115">
+        <v>0</v>
+      </c>
+      <c r="JB115">
         <v>0</v>
       </c>
     </row>
@@ -57198,10 +57198,10 @@
         <v>1</v>
       </c>
       <c r="IW116">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="IX116">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY116">
         <v>1</v>
@@ -57216,10 +57216,10 @@
         <v>1</v>
       </c>
       <c r="JC116">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="JD116">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117" spans="1:264">
@@ -57701,7 +57701,7 @@
         <v>1</v>
       </c>
       <c r="IW117">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX117">
         <v>1</v>
@@ -57719,7 +57719,7 @@
         <v>1</v>
       </c>
       <c r="JC117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD117">
         <v>1</v>
@@ -58204,10 +58204,10 @@
         <v>1</v>
       </c>
       <c r="IW118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY118">
         <v>1</v>
@@ -58222,10 +58222,10 @@
         <v>1</v>
       </c>
       <c r="JC118">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD118">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119" spans="1:264">
@@ -58707,7 +58707,7 @@
         <v>4</v>
       </c>
       <c r="IW119">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="IX119">
         <v>1</v>
@@ -58725,10 +58725,10 @@
         <v>1</v>
       </c>
       <c r="JC119">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="JD119">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120" spans="1:264">
@@ -59210,10 +59210,10 @@
         <v>4</v>
       </c>
       <c r="IW120">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX120">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY120">
         <v>1</v>
@@ -59228,10 +59228,10 @@
         <v>1</v>
       </c>
       <c r="JC120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD120">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121" spans="1:264">
@@ -59713,28 +59713,28 @@
         <v>4</v>
       </c>
       <c r="IW121">
+        <v>1</v>
+      </c>
+      <c r="IX121">
+        <v>1</v>
+      </c>
+      <c r="IY121">
+        <v>0</v>
+      </c>
+      <c r="IZ121">
+        <v>0</v>
+      </c>
+      <c r="JA121">
+        <v>1</v>
+      </c>
+      <c r="JB121">
+        <v>1</v>
+      </c>
+      <c r="JC121">
         <v>5</v>
       </c>
-      <c r="IX121">
+      <c r="JD121">
         <v>5</v>
-      </c>
-      <c r="IY121">
-        <v>1</v>
-      </c>
-      <c r="IZ121">
-        <v>1</v>
-      </c>
-      <c r="JA121">
-        <v>0</v>
-      </c>
-      <c r="JB121">
-        <v>0</v>
-      </c>
-      <c r="JC121">
-        <v>1</v>
-      </c>
-      <c r="JD121">
-        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:264">
@@ -60171,7 +60171,7 @@
         <v>3</v>
       </c>
       <c r="IW122">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY122">
         <v>1</v>
@@ -60179,11 +60179,11 @@
       <c r="JA122">
         <v>1</v>
       </c>
+      <c r="JB122">
+        <v>0</v>
+      </c>
       <c r="JC122">
-        <v>1</v>
-      </c>
-      <c r="JD122">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123" spans="1:264">
@@ -60620,7 +60620,7 @@
         <v>3</v>
       </c>
       <c r="IW123">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="IY123">
         <v>1</v>
@@ -60628,11 +60628,11 @@
       <c r="JA123">
         <v>1</v>
       </c>
+      <c r="JB123">
+        <v>0</v>
+      </c>
       <c r="JC123">
-        <v>1</v>
-      </c>
-      <c r="JD123">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="124" spans="1:264">
@@ -61069,7 +61069,7 @@
         <v>3</v>
       </c>
       <c r="IW124">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY124">
         <v>1</v>
@@ -61077,11 +61077,11 @@
       <c r="JA124">
         <v>1</v>
       </c>
+      <c r="JB124">
+        <v>0</v>
+      </c>
       <c r="JC124">
-        <v>1</v>
-      </c>
-      <c r="JD124">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125" spans="1:264">
@@ -61563,28 +61563,28 @@
         <v>3</v>
       </c>
       <c r="IW125">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX125">
+        <v>1</v>
+      </c>
+      <c r="IY125">
+        <v>1</v>
+      </c>
+      <c r="IZ125">
+        <v>1</v>
+      </c>
+      <c r="JA125">
+        <v>1</v>
+      </c>
+      <c r="JB125">
+        <v>1</v>
+      </c>
+      <c r="JC125">
+        <v>2</v>
+      </c>
+      <c r="JD125">
         <v>7</v>
-      </c>
-      <c r="IY125">
-        <v>1</v>
-      </c>
-      <c r="IZ125">
-        <v>1</v>
-      </c>
-      <c r="JA125">
-        <v>1</v>
-      </c>
-      <c r="JB125">
-        <v>1</v>
-      </c>
-      <c r="JC125">
-        <v>1</v>
-      </c>
-      <c r="JD125">
-        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:264">
@@ -62066,7 +62066,7 @@
         <v>3</v>
       </c>
       <c r="IW126">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="IX126">
         <v>1</v>
@@ -62084,7 +62084,7 @@
         <v>1</v>
       </c>
       <c r="JC126">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="JD126">
         <v>1</v>
@@ -62572,7 +62572,7 @@
         <v>1</v>
       </c>
       <c r="IX127">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY127">
         <v>1</v>
@@ -62590,7 +62590,7 @@
         <v>1</v>
       </c>
       <c r="JD127">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128" spans="1:264">
@@ -63048,7 +63048,7 @@
         <v>3</v>
       </c>
       <c r="IW128">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY128">
         <v>1</v>
@@ -63056,11 +63056,11 @@
       <c r="JA128">
         <v>1</v>
       </c>
+      <c r="JB128">
+        <v>0</v>
+      </c>
       <c r="JC128">
-        <v>1</v>
-      </c>
-      <c r="JD128">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129" spans="1:264">
@@ -63542,10 +63542,10 @@
         <v>1</v>
       </c>
       <c r="IW129">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="IX129">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY129">
         <v>1</v>
@@ -63560,10 +63560,10 @@
         <v>1</v>
       </c>
       <c r="JC129">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="JD129">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130" spans="1:264">
@@ -64045,10 +64045,10 @@
         <v>1</v>
       </c>
       <c r="IW130">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="IX130">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="IY130">
         <v>1</v>
@@ -64063,10 +64063,10 @@
         <v>1</v>
       </c>
       <c r="JC130">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="JD130">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131" spans="1:264">
@@ -64509,7 +64509,7 @@
         <v>1</v>
       </c>
       <c r="IW131">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY131">
         <v>1</v>
@@ -64517,11 +64517,11 @@
       <c r="JA131">
         <v>1</v>
       </c>
+      <c r="JB131">
+        <v>0</v>
+      </c>
       <c r="JC131">
-        <v>1</v>
-      </c>
-      <c r="JD131">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132" spans="1:264">
@@ -64964,7 +64964,7 @@
         <v>1</v>
       </c>
       <c r="IW132">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY132">
         <v>1</v>
@@ -64972,11 +64972,11 @@
       <c r="JA132">
         <v>1</v>
       </c>
+      <c r="JB132">
+        <v>0</v>
+      </c>
       <c r="JC132">
-        <v>1</v>
-      </c>
-      <c r="JD132">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133" spans="1:264">
@@ -65419,19 +65419,19 @@
         <v>1</v>
       </c>
       <c r="IW133">
+        <v>1</v>
+      </c>
+      <c r="IY133">
+        <v>1</v>
+      </c>
+      <c r="JA133">
+        <v>1</v>
+      </c>
+      <c r="JB133">
+        <v>0</v>
+      </c>
+      <c r="JC133">
         <v>7</v>
-      </c>
-      <c r="IY133">
-        <v>1</v>
-      </c>
-      <c r="JA133">
-        <v>1</v>
-      </c>
-      <c r="JC133">
-        <v>1</v>
-      </c>
-      <c r="JD133">
-        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:264">
@@ -65874,19 +65874,19 @@
         <v>5</v>
       </c>
       <c r="IX134">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="IZ134">
         <v>1</v>
       </c>
+      <c r="JA134">
+        <v>0</v>
+      </c>
       <c r="JB134">
         <v>1</v>
       </c>
-      <c r="JC134">
-        <v>0</v>
-      </c>
       <c r="JD134">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135" spans="1:264">
@@ -66329,19 +66329,19 @@
         <v>5</v>
       </c>
       <c r="IX135">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IZ135">
         <v>1</v>
       </c>
+      <c r="JA135">
+        <v>0</v>
+      </c>
       <c r="JB135">
         <v>1</v>
       </c>
-      <c r="JC135">
-        <v>0</v>
-      </c>
       <c r="JD135">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136" spans="1:264">
@@ -66784,19 +66784,19 @@
         <v>5</v>
       </c>
       <c r="IX136">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IZ136">
         <v>1</v>
       </c>
+      <c r="JA136">
+        <v>0</v>
+      </c>
       <c r="JB136">
         <v>1</v>
       </c>
-      <c r="JC136">
-        <v>0</v>
-      </c>
       <c r="JD136">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137" spans="1:264">
@@ -67193,10 +67193,10 @@
       <c r="IN137">
         <v>3</v>
       </c>
-      <c r="JC137">
-        <v>0</v>
-      </c>
-      <c r="JD137">
+      <c r="JA137">
+        <v>0</v>
+      </c>
+      <c r="JB137">
         <v>0</v>
       </c>
     </row>
@@ -67594,10 +67594,10 @@
       <c r="IN138">
         <v>2</v>
       </c>
-      <c r="JC138">
-        <v>0</v>
-      </c>
-      <c r="JD138">
+      <c r="JA138">
+        <v>0</v>
+      </c>
+      <c r="JB138">
         <v>0</v>
       </c>
     </row>
@@ -67995,10 +67995,10 @@
       <c r="IN139">
         <v>2</v>
       </c>
-      <c r="JC139">
-        <v>0</v>
-      </c>
-      <c r="JD139">
+      <c r="JA139">
+        <v>0</v>
+      </c>
+      <c r="JB139">
         <v>0</v>
       </c>
     </row>
@@ -68478,10 +68478,10 @@
         <v>3</v>
       </c>
       <c r="IW140">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX140">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY140">
         <v>1</v>
@@ -68496,10 +68496,10 @@
         <v>1</v>
       </c>
       <c r="JC140">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD140">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141" spans="1:264">
@@ -68978,7 +68978,7 @@
         <v>3</v>
       </c>
       <c r="IW141">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX141">
         <v>1</v>
@@ -68996,7 +68996,7 @@
         <v>1</v>
       </c>
       <c r="JC141">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD141">
         <v>1</v>
@@ -69478,28 +69478,28 @@
         <v>3</v>
       </c>
       <c r="IW142">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX142">
+        <v>1</v>
+      </c>
+      <c r="IY142">
+        <v>1</v>
+      </c>
+      <c r="IZ142">
+        <v>1</v>
+      </c>
+      <c r="JA142">
+        <v>1</v>
+      </c>
+      <c r="JB142">
+        <v>1</v>
+      </c>
+      <c r="JC142">
+        <v>2</v>
+      </c>
+      <c r="JD142">
         <v>7</v>
-      </c>
-      <c r="IY142">
-        <v>1</v>
-      </c>
-      <c r="IZ142">
-        <v>1</v>
-      </c>
-      <c r="JA142">
-        <v>1</v>
-      </c>
-      <c r="JB142">
-        <v>1</v>
-      </c>
-      <c r="JC142">
-        <v>1</v>
-      </c>
-      <c r="JD142">
-        <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:264">
@@ -69978,28 +69978,28 @@
         <v>5</v>
       </c>
       <c r="IW143">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="IX143">
+        <v>1</v>
+      </c>
+      <c r="IY143">
+        <v>1</v>
+      </c>
+      <c r="IZ143">
+        <v>1</v>
+      </c>
+      <c r="JA143">
+        <v>1</v>
+      </c>
+      <c r="JB143">
+        <v>1</v>
+      </c>
+      <c r="JC143">
+        <v>4</v>
+      </c>
+      <c r="JD143">
         <v>5</v>
-      </c>
-      <c r="IY143">
-        <v>1</v>
-      </c>
-      <c r="IZ143">
-        <v>1</v>
-      </c>
-      <c r="JA143">
-        <v>1</v>
-      </c>
-      <c r="JB143">
-        <v>1</v>
-      </c>
-      <c r="JC143">
-        <v>1</v>
-      </c>
-      <c r="JD143">
-        <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:264">
@@ -70481,25 +70481,25 @@
         <v>1</v>
       </c>
       <c r="IX144">
+        <v>1</v>
+      </c>
+      <c r="IY144">
+        <v>1</v>
+      </c>
+      <c r="IZ144">
+        <v>1</v>
+      </c>
+      <c r="JA144">
+        <v>1</v>
+      </c>
+      <c r="JB144">
+        <v>1</v>
+      </c>
+      <c r="JC144">
+        <v>1</v>
+      </c>
+      <c r="JD144">
         <v>6</v>
-      </c>
-      <c r="IY144">
-        <v>1</v>
-      </c>
-      <c r="IZ144">
-        <v>1</v>
-      </c>
-      <c r="JA144">
-        <v>1</v>
-      </c>
-      <c r="JB144">
-        <v>1</v>
-      </c>
-      <c r="JC144">
-        <v>1</v>
-      </c>
-      <c r="JD144">
-        <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:264">
@@ -70978,10 +70978,10 @@
         <v>5</v>
       </c>
       <c r="IW145">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX145">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="IY145">
         <v>1</v>
@@ -70996,10 +70996,10 @@
         <v>1</v>
       </c>
       <c r="JC145">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD145">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="146" spans="1:264">
@@ -71478,10 +71478,10 @@
         <v>5</v>
       </c>
       <c r="IW146">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="IX146">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY146">
         <v>1</v>
@@ -71496,10 +71496,10 @@
         <v>1</v>
       </c>
       <c r="JC146">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="JD146">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147" spans="1:264">
@@ -71978,28 +71978,28 @@
         <v>5</v>
       </c>
       <c r="IW147">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX147">
+        <v>1</v>
+      </c>
+      <c r="IY147">
+        <v>1</v>
+      </c>
+      <c r="IZ147">
+        <v>1</v>
+      </c>
+      <c r="JA147">
+        <v>1</v>
+      </c>
+      <c r="JB147">
+        <v>1</v>
+      </c>
+      <c r="JC147">
+        <v>2</v>
+      </c>
+      <c r="JD147">
         <v>5</v>
-      </c>
-      <c r="IY147">
-        <v>1</v>
-      </c>
-      <c r="IZ147">
-        <v>1</v>
-      </c>
-      <c r="JA147">
-        <v>1</v>
-      </c>
-      <c r="JB147">
-        <v>1</v>
-      </c>
-      <c r="JC147">
-        <v>1</v>
-      </c>
-      <c r="JD147">
-        <v>1</v>
       </c>
     </row>
     <row r="148" spans="1:264">
@@ -72478,28 +72478,28 @@
         <v>5</v>
       </c>
       <c r="IW148">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX148">
+        <v>1</v>
+      </c>
+      <c r="IY148">
+        <v>1</v>
+      </c>
+      <c r="IZ148">
+        <v>1</v>
+      </c>
+      <c r="JA148">
+        <v>1</v>
+      </c>
+      <c r="JB148">
+        <v>1</v>
+      </c>
+      <c r="JC148">
+        <v>2</v>
+      </c>
+      <c r="JD148">
         <v>7</v>
-      </c>
-      <c r="IY148">
-        <v>1</v>
-      </c>
-      <c r="IZ148">
-        <v>1</v>
-      </c>
-      <c r="JA148">
-        <v>1</v>
-      </c>
-      <c r="JB148">
-        <v>1</v>
-      </c>
-      <c r="JC148">
-        <v>1</v>
-      </c>
-      <c r="JD148">
-        <v>1</v>
       </c>
     </row>
     <row r="149" spans="1:264">
@@ -72981,10 +72981,10 @@
         <v>3</v>
       </c>
       <c r="IW149">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="IX149">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY149">
         <v>1</v>
@@ -72999,10 +72999,10 @@
         <v>1</v>
       </c>
       <c r="JC149">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="JD149">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150" spans="1:264">
@@ -73484,10 +73484,10 @@
         <v>3</v>
       </c>
       <c r="IW150">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX150">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY150">
         <v>1</v>
@@ -73502,10 +73502,10 @@
         <v>1</v>
       </c>
       <c r="JC150">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD150">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151" spans="1:264">
@@ -73987,10 +73987,10 @@
         <v>3</v>
       </c>
       <c r="IW151">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX151">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="IY151">
         <v>1</v>
@@ -74005,10 +74005,10 @@
         <v>1</v>
       </c>
       <c r="JC151">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD151">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="152" spans="1:264">
@@ -74417,10 +74417,10 @@
       <c r="IN152">
         <v>2</v>
       </c>
-      <c r="JC152">
-        <v>0</v>
-      </c>
-      <c r="JD152">
+      <c r="JA152">
+        <v>0</v>
+      </c>
+      <c r="JB152">
         <v>0</v>
       </c>
     </row>
@@ -74855,7 +74855,7 @@
         <v>1</v>
       </c>
       <c r="IW153">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="IY153">
         <v>1</v>
@@ -74863,11 +74863,11 @@
       <c r="JA153">
         <v>1</v>
       </c>
+      <c r="JB153">
+        <v>0</v>
+      </c>
       <c r="JC153">
-        <v>1</v>
-      </c>
-      <c r="JD153">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154" spans="1:264">
@@ -75276,10 +75276,10 @@
       <c r="IN154">
         <v>2</v>
       </c>
-      <c r="JC154">
-        <v>0</v>
-      </c>
-      <c r="JD154">
+      <c r="JA154">
+        <v>0</v>
+      </c>
+      <c r="JB154">
         <v>0</v>
       </c>
     </row>
@@ -75759,28 +75759,28 @@
         <v>1</v>
       </c>
       <c r="IW155">
+        <v>1</v>
+      </c>
+      <c r="IX155">
+        <v>1</v>
+      </c>
+      <c r="IY155">
+        <v>1</v>
+      </c>
+      <c r="IZ155">
+        <v>1</v>
+      </c>
+      <c r="JA155">
+        <v>1</v>
+      </c>
+      <c r="JB155">
+        <v>1</v>
+      </c>
+      <c r="JC155">
         <v>7</v>
       </c>
-      <c r="IX155">
-        <v>2</v>
-      </c>
-      <c r="IY155">
-        <v>1</v>
-      </c>
-      <c r="IZ155">
-        <v>1</v>
-      </c>
-      <c r="JA155">
-        <v>1</v>
-      </c>
-      <c r="JB155">
-        <v>1</v>
-      </c>
-      <c r="JC155">
-        <v>1</v>
-      </c>
       <c r="JD155">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="156" spans="1:264">
@@ -76262,7 +76262,7 @@
         <v>1</v>
       </c>
       <c r="IX156">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY156">
         <v>1</v>
@@ -76280,7 +76280,7 @@
         <v>1</v>
       </c>
       <c r="JD156">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157" spans="1:264">
@@ -76710,10 +76710,10 @@
       <c r="IN157">
         <v>2</v>
       </c>
-      <c r="JC157">
-        <v>0</v>
-      </c>
-      <c r="JD157">
+      <c r="JA157">
+        <v>0</v>
+      </c>
+      <c r="JB157">
         <v>0</v>
       </c>
     </row>
@@ -77229,25 +77229,25 @@
         <v>3</v>
       </c>
       <c r="IW158">
+        <v>1</v>
+      </c>
+      <c r="IX158">
+        <v>1</v>
+      </c>
+      <c r="IY158">
+        <v>1</v>
+      </c>
+      <c r="IZ158">
+        <v>1</v>
+      </c>
+      <c r="JA158">
+        <v>1</v>
+      </c>
+      <c r="JB158">
+        <v>1</v>
+      </c>
+      <c r="JC158">
         <v>6</v>
-      </c>
-      <c r="IX158">
-        <v>1</v>
-      </c>
-      <c r="IY158">
-        <v>1</v>
-      </c>
-      <c r="IZ158">
-        <v>1</v>
-      </c>
-      <c r="JA158">
-        <v>1</v>
-      </c>
-      <c r="JB158">
-        <v>1</v>
-      </c>
-      <c r="JC158">
-        <v>1</v>
       </c>
       <c r="JD158">
         <v>1</v>
@@ -77765,10 +77765,10 @@
         <v>3</v>
       </c>
       <c r="IW159">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX159">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY159">
         <v>1</v>
@@ -77783,10 +77783,10 @@
         <v>1</v>
       </c>
       <c r="JC159">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD159">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160" spans="1:264">
@@ -78301,28 +78301,28 @@
         <v>3</v>
       </c>
       <c r="IW160">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX160">
+        <v>1</v>
+      </c>
+      <c r="IY160">
+        <v>1</v>
+      </c>
+      <c r="IZ160">
+        <v>1</v>
+      </c>
+      <c r="JA160">
+        <v>1</v>
+      </c>
+      <c r="JB160">
+        <v>1</v>
+      </c>
+      <c r="JC160">
+        <v>2</v>
+      </c>
+      <c r="JD160">
         <v>7</v>
-      </c>
-      <c r="IY160">
-        <v>1</v>
-      </c>
-      <c r="IZ160">
-        <v>1</v>
-      </c>
-      <c r="JA160">
-        <v>1</v>
-      </c>
-      <c r="JB160">
-        <v>1</v>
-      </c>
-      <c r="JC160">
-        <v>1</v>
-      </c>
-      <c r="JD160">
-        <v>1</v>
       </c>
     </row>
     <row r="161" spans="1:264">
@@ -78804,10 +78804,10 @@
         <v>3</v>
       </c>
       <c r="IW161">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX161">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY161">
         <v>1</v>
@@ -78822,10 +78822,10 @@
         <v>1</v>
       </c>
       <c r="JC161">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD161">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162" spans="1:264">
@@ -79307,28 +79307,28 @@
         <v>3</v>
       </c>
       <c r="IW162">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="IX162">
+        <v>1</v>
+      </c>
+      <c r="IY162">
+        <v>1</v>
+      </c>
+      <c r="IZ162">
+        <v>1</v>
+      </c>
+      <c r="JA162">
+        <v>1</v>
+      </c>
+      <c r="JB162">
+        <v>1</v>
+      </c>
+      <c r="JC162">
+        <v>4</v>
+      </c>
+      <c r="JD162">
         <v>5</v>
-      </c>
-      <c r="IY162">
-        <v>1</v>
-      </c>
-      <c r="IZ162">
-        <v>1</v>
-      </c>
-      <c r="JA162">
-        <v>1</v>
-      </c>
-      <c r="JB162">
-        <v>1</v>
-      </c>
-      <c r="JC162">
-        <v>1</v>
-      </c>
-      <c r="JD162">
-        <v>1</v>
       </c>
     </row>
     <row r="163" spans="1:264">
@@ -79810,28 +79810,28 @@
         <v>3</v>
       </c>
       <c r="IW163">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX163">
+        <v>1</v>
+      </c>
+      <c r="IY163">
+        <v>1</v>
+      </c>
+      <c r="IZ163">
+        <v>1</v>
+      </c>
+      <c r="JA163">
+        <v>1</v>
+      </c>
+      <c r="JB163">
+        <v>1</v>
+      </c>
+      <c r="JC163">
+        <v>2</v>
+      </c>
+      <c r="JD163">
         <v>7</v>
-      </c>
-      <c r="IY163">
-        <v>1</v>
-      </c>
-      <c r="IZ163">
-        <v>1</v>
-      </c>
-      <c r="JA163">
-        <v>1</v>
-      </c>
-      <c r="JB163">
-        <v>1</v>
-      </c>
-      <c r="JC163">
-        <v>1</v>
-      </c>
-      <c r="JD163">
-        <v>1</v>
       </c>
     </row>
     <row r="164" spans="1:264">
@@ -80261,10 +80261,10 @@
       <c r="IN164">
         <v>2</v>
       </c>
-      <c r="JC164">
-        <v>0</v>
-      </c>
-      <c r="JD164">
+      <c r="JA164">
+        <v>0</v>
+      </c>
+      <c r="JB164">
         <v>0</v>
       </c>
     </row>
@@ -80744,10 +80744,10 @@
         <v>1</v>
       </c>
       <c r="IW165">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="IX165">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY165">
         <v>1</v>
@@ -80762,10 +80762,10 @@
         <v>1</v>
       </c>
       <c r="JC165">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="JD165">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166" spans="1:264">
@@ -81244,7 +81244,7 @@
         <v>1</v>
       </c>
       <c r="IW166">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX166">
         <v>1</v>
@@ -81262,7 +81262,7 @@
         <v>1</v>
       </c>
       <c r="JC166">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD166">
         <v>1</v>
@@ -81744,28 +81744,28 @@
         <v>1</v>
       </c>
       <c r="IW167">
+        <v>1</v>
+      </c>
+      <c r="IX167">
+        <v>1</v>
+      </c>
+      <c r="IY167">
+        <v>1</v>
+      </c>
+      <c r="IZ167">
+        <v>1</v>
+      </c>
+      <c r="JA167">
+        <v>1</v>
+      </c>
+      <c r="JB167">
+        <v>1</v>
+      </c>
+      <c r="JC167">
         <v>6</v>
       </c>
-      <c r="IX167">
+      <c r="JD167">
         <v>5</v>
-      </c>
-      <c r="IY167">
-        <v>1</v>
-      </c>
-      <c r="IZ167">
-        <v>1</v>
-      </c>
-      <c r="JA167">
-        <v>1</v>
-      </c>
-      <c r="JB167">
-        <v>1</v>
-      </c>
-      <c r="JC167">
-        <v>1</v>
-      </c>
-      <c r="JD167">
-        <v>1</v>
       </c>
     </row>
     <row r="168" spans="1:264">
@@ -82244,28 +82244,28 @@
         <v>1</v>
       </c>
       <c r="IW168">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX168">
+        <v>1</v>
+      </c>
+      <c r="IY168">
+        <v>1</v>
+      </c>
+      <c r="IZ168">
+        <v>1</v>
+      </c>
+      <c r="JA168">
+        <v>1</v>
+      </c>
+      <c r="JB168">
+        <v>1</v>
+      </c>
+      <c r="JC168">
+        <v>2</v>
+      </c>
+      <c r="JD168">
         <v>5</v>
-      </c>
-      <c r="IY168">
-        <v>1</v>
-      </c>
-      <c r="IZ168">
-        <v>1</v>
-      </c>
-      <c r="JA168">
-        <v>1</v>
-      </c>
-      <c r="JB168">
-        <v>1</v>
-      </c>
-      <c r="JC168">
-        <v>1</v>
-      </c>
-      <c r="JD168">
-        <v>1</v>
       </c>
     </row>
     <row r="169" spans="1:264">
@@ -82744,10 +82744,10 @@
         <v>1</v>
       </c>
       <c r="IW169">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX169">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY169">
         <v>1</v>
@@ -82762,10 +82762,10 @@
         <v>1</v>
       </c>
       <c r="JC169">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD169">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="170" spans="1:264">
@@ -83244,10 +83244,10 @@
         <v>3</v>
       </c>
       <c r="IW170">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX170">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY170">
         <v>1</v>
@@ -83262,10 +83262,10 @@
         <v>1</v>
       </c>
       <c r="JC170">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD170">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171" spans="1:264">
@@ -83744,10 +83744,10 @@
         <v>3</v>
       </c>
       <c r="IW171">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="IX171">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="IY171">
         <v>1</v>
@@ -83762,10 +83762,10 @@
         <v>1</v>
       </c>
       <c r="JC171">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="JD171">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172" spans="1:264">
@@ -84220,7 +84220,7 @@
         <v>1</v>
       </c>
       <c r="IW172">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY172">
         <v>1</v>
@@ -84228,11 +84228,11 @@
       <c r="JA172">
         <v>1</v>
       </c>
+      <c r="JB172">
+        <v>0</v>
+      </c>
       <c r="JC172">
-        <v>1</v>
-      </c>
-      <c r="JD172">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173" spans="1:264">
@@ -84666,7 +84666,7 @@
         <v>3</v>
       </c>
       <c r="IW173">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY173">
         <v>1</v>
@@ -84674,11 +84674,11 @@
       <c r="JA173">
         <v>1</v>
       </c>
+      <c r="JB173">
+        <v>0</v>
+      </c>
       <c r="JC173">
-        <v>1</v>
-      </c>
-      <c r="JD173">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174" spans="1:264">
@@ -85112,7 +85112,7 @@
         <v>3</v>
       </c>
       <c r="IW174">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="IY174">
         <v>1</v>
@@ -85120,11 +85120,11 @@
       <c r="JA174">
         <v>1</v>
       </c>
+      <c r="JB174">
+        <v>0</v>
+      </c>
       <c r="JC174">
-        <v>1</v>
-      </c>
-      <c r="JD174">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175" spans="1:264">
@@ -85558,7 +85558,7 @@
         <v>3</v>
       </c>
       <c r="IW175">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY175">
         <v>1</v>
@@ -85566,11 +85566,11 @@
       <c r="JA175">
         <v>1</v>
       </c>
+      <c r="JB175">
+        <v>0</v>
+      </c>
       <c r="JC175">
-        <v>1</v>
-      </c>
-      <c r="JD175">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176" spans="1:264">
@@ -86049,10 +86049,10 @@
         <v>1</v>
       </c>
       <c r="IW176">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX176">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY176">
         <v>1</v>
@@ -86067,10 +86067,10 @@
         <v>1</v>
       </c>
       <c r="JC176">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD176">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177" spans="1:264">
@@ -86525,7 +86525,7 @@
         <v>1</v>
       </c>
       <c r="IW177">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY177">
         <v>1</v>
@@ -86533,11 +86533,11 @@
       <c r="JA177">
         <v>1</v>
       </c>
+      <c r="JB177">
+        <v>0</v>
+      </c>
       <c r="JC177">
-        <v>1</v>
-      </c>
-      <c r="JD177">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="178" spans="1:264">
@@ -87516,10 +87516,10 @@
         <v>1</v>
       </c>
       <c r="IW179">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IX179">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IY179">
         <v>1</v>
@@ -87534,10 +87534,10 @@
         <v>1</v>
       </c>
       <c r="JC179">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JD179">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180" spans="1:264">
@@ -88016,28 +88016,28 @@
         <v>1</v>
       </c>
       <c r="IW180">
+        <v>1</v>
+      </c>
+      <c r="IX180">
+        <v>1</v>
+      </c>
+      <c r="IY180">
+        <v>1</v>
+      </c>
+      <c r="IZ180">
+        <v>1</v>
+      </c>
+      <c r="JA180">
+        <v>1</v>
+      </c>
+      <c r="JB180">
+        <v>1</v>
+      </c>
+      <c r="JC180">
         <v>7</v>
       </c>
-      <c r="IX180">
+      <c r="JD180">
         <v>7</v>
-      </c>
-      <c r="IY180">
-        <v>1</v>
-      </c>
-      <c r="IZ180">
-        <v>1</v>
-      </c>
-      <c r="JA180">
-        <v>1</v>
-      </c>
-      <c r="JB180">
-        <v>1</v>
-      </c>
-      <c r="JC180">
-        <v>1</v>
-      </c>
-      <c r="JD180">
-        <v>1</v>
       </c>
     </row>
     <row r="181" spans="1:264">
@@ -88997,11 +88997,11 @@
       <c r="IZ182">
         <v>1</v>
       </c>
+      <c r="JA182">
+        <v>0</v>
+      </c>
       <c r="JB182">
         <v>1</v>
-      </c>
-      <c r="JC182">
-        <v>0</v>
       </c>
       <c r="JD182">
         <v>1</v>
@@ -89459,7 +89459,7 @@
         <v>5</v>
       </c>
       <c r="IW183">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="IY183">
         <v>1</v>
@@ -89467,11 +89467,11 @@
       <c r="JA183">
         <v>1</v>
       </c>
+      <c r="JB183">
+        <v>0</v>
+      </c>
       <c r="JC183">
-        <v>1</v>
-      </c>
-      <c r="JD183">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="184" spans="1:264">
@@ -89926,19 +89926,19 @@
         <v>4</v>
       </c>
       <c r="IX184">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="IZ184">
         <v>1</v>
       </c>
+      <c r="JA184">
+        <v>0</v>
+      </c>
       <c r="JB184">
         <v>1</v>
       </c>
-      <c r="JC184">
-        <v>0</v>
-      </c>
       <c r="JD184">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/dataset2026.xlsx
+++ b/dataset2026.xlsx
@@ -3342,7 +3342,7 @@
         <v>0</v>
       </c>
       <c r="JC2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:264">
@@ -5117,7 +5117,7 @@
         <v>1</v>
       </c>
       <c r="JD6">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:264">
@@ -5994,7 +5994,7 @@
         <v>1</v>
       </c>
       <c r="JD8">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:264">
@@ -6449,7 +6449,7 @@
         <v>1</v>
       </c>
       <c r="JD9">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:264">
@@ -6904,7 +6904,7 @@
         <v>1</v>
       </c>
       <c r="JD10">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:264">
@@ -8754,7 +8754,7 @@
         <v>2</v>
       </c>
       <c r="JD14">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:264">
@@ -12690,7 +12690,7 @@
         <v>0</v>
       </c>
       <c r="JC23">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:264">
@@ -13588,7 +13588,7 @@
         <v>0</v>
       </c>
       <c r="JC25">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:264">
@@ -15600,7 +15600,7 @@
         <v>1</v>
       </c>
       <c r="JD29">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:264">
@@ -16103,7 +16103,7 @@
         <v>2</v>
       </c>
       <c r="JD30">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:264">
@@ -16603,10 +16603,10 @@
         <v>1</v>
       </c>
       <c r="JC31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="JD31">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:264">
@@ -17106,10 +17106,10 @@
         <v>1</v>
       </c>
       <c r="JC32">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="JD32">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:264">
@@ -18046,7 +18046,7 @@
         <v>1</v>
       </c>
       <c r="JC34">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="JD34">
         <v>2</v>
@@ -21698,10 +21698,10 @@
         <v>1</v>
       </c>
       <c r="JC42">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="JD42">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:264">
@@ -23677,7 +23677,7 @@
         <v>1</v>
       </c>
       <c r="JC46">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="JD46">
         <v>2</v>
@@ -24183,7 +24183,7 @@
         <v>3</v>
       </c>
       <c r="JD47">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:264">
@@ -26665,10 +26665,10 @@
         <v>1</v>
       </c>
       <c r="JC52">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="JD52">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" spans="1:264">
@@ -27114,7 +27114,7 @@
         <v>0</v>
       </c>
       <c r="JC53">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:264">
@@ -31970,10 +31970,10 @@
         <v>1</v>
       </c>
       <c r="JC63">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="JD63">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:264">
@@ -32970,10 +32970,10 @@
         <v>1</v>
       </c>
       <c r="JC65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="JD65">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:264">
@@ -33970,7 +33970,7 @@
         <v>1</v>
       </c>
       <c r="JC67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="JD67">
         <v>1</v>
@@ -34473,7 +34473,7 @@
         <v>1</v>
       </c>
       <c r="JD68">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:264">
@@ -35937,7 +35937,7 @@
         <v>1</v>
       </c>
       <c r="JC71">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="JD71">
         <v>2</v>
@@ -40113,7 +40113,7 @@
         <v>2</v>
       </c>
       <c r="JD80">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81" spans="1:264">
@@ -40613,7 +40613,7 @@
         <v>2</v>
       </c>
       <c r="JD81">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:264">
@@ -41110,7 +41110,7 @@
         <v>1</v>
       </c>
       <c r="JC82">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="JD82">
         <v>2</v>
@@ -43199,7 +43199,7 @@
         <v>0</v>
       </c>
       <c r="JC87">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88" spans="1:264">
@@ -44112,7 +44112,7 @@
         <v>1</v>
       </c>
       <c r="JD89">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90" spans="1:264">
@@ -47624,7 +47624,7 @@
         <v>1</v>
       </c>
       <c r="JC96">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="JD96">
         <v>1</v>
@@ -48127,7 +48127,7 @@
         <v>1</v>
       </c>
       <c r="JC97">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="JD97">
         <v>2</v>
@@ -49028,7 +49028,7 @@
         <v>0</v>
       </c>
       <c r="JC99">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:264">
@@ -50480,7 +50480,7 @@
         <v>1</v>
       </c>
       <c r="JC102">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="JD102">
         <v>2</v>
@@ -53498,7 +53498,7 @@
         <v>1</v>
       </c>
       <c r="JC108">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="JD108">
         <v>2</v>
@@ -54001,7 +54001,7 @@
         <v>1</v>
       </c>
       <c r="JC109">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="JD109">
         <v>2</v>
@@ -59731,10 +59731,10 @@
         <v>1</v>
       </c>
       <c r="JC121">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="JD121">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="122" spans="1:264">
@@ -60632,7 +60632,7 @@
         <v>0</v>
       </c>
       <c r="JC123">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124" spans="1:264">
@@ -61584,7 +61584,7 @@
         <v>2</v>
       </c>
       <c r="JD125">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="126" spans="1:264">
@@ -62084,7 +62084,7 @@
         <v>1</v>
       </c>
       <c r="JC126">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="JD126">
         <v>1</v>
@@ -63560,7 +63560,7 @@
         <v>1</v>
       </c>
       <c r="JC129">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="JD129">
         <v>2</v>
@@ -65431,7 +65431,7 @@
         <v>0</v>
       </c>
       <c r="JC133">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="134" spans="1:264">
@@ -65886,7 +65886,7 @@
         <v>1</v>
       </c>
       <c r="JD134">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="135" spans="1:264">
@@ -69499,7 +69499,7 @@
         <v>2</v>
       </c>
       <c r="JD142">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="143" spans="1:264">
@@ -69996,10 +69996,10 @@
         <v>1</v>
       </c>
       <c r="JC143">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="JD143">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="144" spans="1:264">
@@ -70499,7 +70499,7 @@
         <v>1</v>
       </c>
       <c r="JD144">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:264">
@@ -70999,7 +70999,7 @@
         <v>2</v>
       </c>
       <c r="JD145">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="146" spans="1:264">
@@ -71999,7 +71999,7 @@
         <v>2</v>
       </c>
       <c r="JD147">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="148" spans="1:264">
@@ -72499,7 +72499,7 @@
         <v>2</v>
       </c>
       <c r="JD148">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="149" spans="1:264">
@@ -75777,7 +75777,7 @@
         <v>1</v>
       </c>
       <c r="JC155">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="JD155">
         <v>2</v>
@@ -77247,7 +77247,7 @@
         <v>1</v>
       </c>
       <c r="JC158">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="JD158">
         <v>1</v>
@@ -78322,7 +78322,7 @@
         <v>2</v>
       </c>
       <c r="JD160">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="161" spans="1:264">
@@ -79325,10 +79325,10 @@
         <v>1</v>
       </c>
       <c r="JC162">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="JD162">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="163" spans="1:264">
@@ -79831,7 +79831,7 @@
         <v>2</v>
       </c>
       <c r="JD163">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="164" spans="1:264">
@@ -80762,7 +80762,7 @@
         <v>1</v>
       </c>
       <c r="JC165">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="JD165">
         <v>2</v>
@@ -81762,10 +81762,10 @@
         <v>1</v>
       </c>
       <c r="JC167">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="JD167">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="168" spans="1:264">
@@ -82265,7 +82265,7 @@
         <v>2</v>
       </c>
       <c r="JD168">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="169" spans="1:264">
@@ -88034,10 +88034,10 @@
         <v>1</v>
       </c>
       <c r="JC180">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="JD180">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="181" spans="1:264">
@@ -89471,7 +89471,7 @@
         <v>0</v>
       </c>
       <c r="JC183">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184" spans="1:264">

--- a/dataset2026.xlsx
+++ b/dataset2026.xlsx
@@ -3342,7 +3342,7 @@
         <v>0</v>
       </c>
       <c r="JC2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:264">
@@ -5117,7 +5117,7 @@
         <v>1</v>
       </c>
       <c r="JD6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:264">
@@ -5994,7 +5994,7 @@
         <v>1</v>
       </c>
       <c r="JD8">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:264">
@@ -6449,7 +6449,7 @@
         <v>1</v>
       </c>
       <c r="JD9">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:264">
@@ -6904,7 +6904,7 @@
         <v>1</v>
       </c>
       <c r="JD10">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:264">
@@ -8754,7 +8754,7 @@
         <v>2</v>
       </c>
       <c r="JD14">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:264">
@@ -12690,7 +12690,7 @@
         <v>0</v>
       </c>
       <c r="JC23">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:264">
@@ -13588,7 +13588,7 @@
         <v>0</v>
       </c>
       <c r="JC25">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:264">
@@ -15600,7 +15600,7 @@
         <v>1</v>
       </c>
       <c r="JD29">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:264">
@@ -16103,7 +16103,7 @@
         <v>2</v>
       </c>
       <c r="JD30">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:264">
@@ -16603,10 +16603,10 @@
         <v>1</v>
       </c>
       <c r="JC31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="JD31">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:264">
@@ -17109,7 +17109,7 @@
         <v>1</v>
       </c>
       <c r="JD32">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:264">
@@ -18046,7 +18046,7 @@
         <v>1</v>
       </c>
       <c r="JC34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="JD34">
         <v>2</v>
@@ -21701,7 +21701,7 @@
         <v>1</v>
       </c>
       <c r="JD42">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:264">
@@ -24183,7 +24183,7 @@
         <v>3</v>
       </c>
       <c r="JD47">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:264">
@@ -26668,7 +26668,7 @@
         <v>1</v>
       </c>
       <c r="JD52">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:264">
@@ -27114,7 +27114,7 @@
         <v>0</v>
       </c>
       <c r="JC53">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:264">
@@ -31970,10 +31970,10 @@
         <v>1</v>
       </c>
       <c r="JC63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="JD63">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64" spans="1:264">
@@ -32970,10 +32970,10 @@
         <v>1</v>
       </c>
       <c r="JC65">
+        <v>4</v>
+      </c>
+      <c r="JD65">
         <v>5</v>
-      </c>
-      <c r="JD65">
-        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:264">
@@ -33970,7 +33970,7 @@
         <v>1</v>
       </c>
       <c r="JC67">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="JD67">
         <v>1</v>
@@ -34473,7 +34473,7 @@
         <v>1</v>
       </c>
       <c r="JD68">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:264">
@@ -35937,7 +35937,7 @@
         <v>1</v>
       </c>
       <c r="JC71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="JD71">
         <v>2</v>
@@ -40113,7 +40113,7 @@
         <v>2</v>
       </c>
       <c r="JD80">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:264">
@@ -40613,7 +40613,7 @@
         <v>2</v>
       </c>
       <c r="JD81">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82" spans="1:264">
@@ -41110,7 +41110,7 @@
         <v>1</v>
       </c>
       <c r="JC82">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="JD82">
         <v>2</v>
@@ -43199,7 +43199,7 @@
         <v>0</v>
       </c>
       <c r="JC87">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:264">
@@ -44112,7 +44112,7 @@
         <v>1</v>
       </c>
       <c r="JD89">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:264">
@@ -48127,7 +48127,7 @@
         <v>1</v>
       </c>
       <c r="JC97">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="JD97">
         <v>2</v>
@@ -49028,7 +49028,7 @@
         <v>0</v>
       </c>
       <c r="JC99">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100" spans="1:264">
@@ -50480,7 +50480,7 @@
         <v>1</v>
       </c>
       <c r="JC102">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="JD102">
         <v>2</v>
@@ -54001,7 +54001,7 @@
         <v>1</v>
       </c>
       <c r="JC109">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="JD109">
         <v>2</v>
@@ -59731,10 +59731,10 @@
         <v>1</v>
       </c>
       <c r="JC121">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="JD121">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122" spans="1:264">
@@ -60632,7 +60632,7 @@
         <v>0</v>
       </c>
       <c r="JC123">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:264">
@@ -61584,7 +61584,7 @@
         <v>2</v>
       </c>
       <c r="JD125">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:264">
@@ -63560,7 +63560,7 @@
         <v>1</v>
       </c>
       <c r="JC129">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="JD129">
         <v>2</v>
@@ -65431,7 +65431,7 @@
         <v>0</v>
       </c>
       <c r="JC133">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:264">
@@ -65886,7 +65886,7 @@
         <v>1</v>
       </c>
       <c r="JD134">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:264">
@@ -69499,7 +69499,7 @@
         <v>2</v>
       </c>
       <c r="JD142">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:264">
@@ -69999,7 +69999,7 @@
         <v>1</v>
       </c>
       <c r="JD143">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144" spans="1:264">
@@ -70499,7 +70499,7 @@
         <v>1</v>
       </c>
       <c r="JD144">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="145" spans="1:264">
@@ -70999,7 +70999,7 @@
         <v>2</v>
       </c>
       <c r="JD145">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:264">
@@ -71999,7 +71999,7 @@
         <v>2</v>
       </c>
       <c r="JD147">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148" spans="1:264">
@@ -72499,7 +72499,7 @@
         <v>2</v>
       </c>
       <c r="JD148">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:264">
@@ -75777,7 +75777,7 @@
         <v>1</v>
       </c>
       <c r="JC155">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="JD155">
         <v>2</v>
@@ -77247,7 +77247,7 @@
         <v>1</v>
       </c>
       <c r="JC158">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="JD158">
         <v>1</v>
@@ -78322,7 +78322,7 @@
         <v>2</v>
       </c>
       <c r="JD160">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:264">
@@ -79325,10 +79325,10 @@
         <v>1</v>
       </c>
       <c r="JC162">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="JD162">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163" spans="1:264">
@@ -79831,7 +79831,7 @@
         <v>2</v>
       </c>
       <c r="JD163">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:264">
@@ -81762,7 +81762,7 @@
         <v>1</v>
       </c>
       <c r="JC167">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="JD167">
         <v>4</v>
@@ -82265,7 +82265,7 @@
         <v>2</v>
       </c>
       <c r="JD168">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="169" spans="1:264">
@@ -88034,10 +88034,10 @@
         <v>1</v>
       </c>
       <c r="JC180">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="JD180">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181" spans="1:264">
